--- a/reports/content/ta/2026-05-15_sync_report.xlsx
+++ b/reports/content/ta/2026-05-15_sync_report.xlsx
@@ -462,13 +462,13 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>572</v>
+        <v>552</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>6366</v>
+        <v>6386</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.2% of prev</t>
+          <t>8.0% of prev</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -658,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G573"/>
+  <dimension ref="A1:G553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -724,12 +724,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">ஊதாப்பூ பார்க்கலாம் </t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -757,12 +757,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">உரலில் எள்ளை இடிக்கலாம் உருண்டையாகப் பிடிக்கலாம் உறவுக்கெல்லாம் கொடுக்கலாம் </t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -790,12 +790,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">ஊர்வலமாய்ப் போகலாம் </t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -823,12 +823,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">ஊதல் ஊதி மகிழலாம் </t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -856,12 +856,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">ஓடும் வண்டி ஒன்றிலே </t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -889,12 +889,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">ஒட்டகம் ஓநாய் அருகிலே  </t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -922,12 +922,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">ஓணான் தம்பி கூடவே  </t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -955,12 +955,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">அம்மா இங்கே வா வா </t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -988,12 +988,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">ஆசை முத்தம் தா தா </t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1021,12 +1021,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">ஊரில் யாவர் உள்ளார் ? </t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1054,12 +1054,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">இலையில் சோறு போட்டு </t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1087,12 +1087,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">﻿உன்னைப் போன்ற நல்லார் </t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1120,12 +1120,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">என்னால் உனக்குத் தொல்லை </t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1153,12 +1153,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">ஐயமின்றிச் சொல்வேன் </t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1186,12 +1186,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">ஓதும் செயலே நலமாம் </t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1219,12 +1219,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">ஒற்றுமை என்றும் பலமாம் </t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1252,12 +1252,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">க் </t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1285,12 +1285,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">கொக்கு  </t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1318,12 +1318,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">முக்காலி  </t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1351,12 +1351,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">தக்காளி </t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1384,12 +1384,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">ச்  </t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1417,12 +1417,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">அச்சாணி  </t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1450,12 +1450,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">குச்சி </t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1483,12 +1483,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">தட்டு  </t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1516,12 +1516,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">ட்  </t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1549,12 +1549,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">சட்டை  </t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1582,12 +1582,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">சுத்தி  </t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1615,12 +1615,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">முட்டை </t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1648,12 +1648,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">த் </t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1681,12 +1681,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
         <is>
           <t xml:space="preserve">நத்தை  </t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1714,12 +1714,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
         <is>
           <t xml:space="preserve">வாத்து  </t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1747,12 +1747,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
         <is>
           <t xml:space="preserve">ங் </t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1780,12 +1780,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
         <is>
           <t xml:space="preserve">நுங்கு  </t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1813,12 +1813,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
         <is>
           <t xml:space="preserve">பஞ்சு  </t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1846,12 +1846,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">சிங்கம் </t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1879,12 +1879,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
         <is>
           <t xml:space="preserve">ஞ் </t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1912,12 +1912,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
         <is>
           <t xml:space="preserve">சங்கு  </t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1945,12 +1945,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
         <is>
           <t xml:space="preserve">மஞ்சள் </t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1978,12 +1978,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
         <is>
           <t xml:space="preserve">இஞ்சி   </t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2011,12 +2011,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
         <is>
           <t xml:space="preserve">ண் </t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2044,12 +2044,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
         <is>
           <t xml:space="preserve">பூண்டு </t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2077,12 +2077,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
         <is>
           <t xml:space="preserve">நண்டு  </t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2110,12 +2110,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
         <is>
           <t xml:space="preserve">ந்  </t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2143,12 +2143,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
         <is>
           <t xml:space="preserve">வண்டு </t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2176,12 +2176,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
         <is>
           <t xml:space="preserve">முந்திரி  </t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2209,12 +2209,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
         <is>
           <t xml:space="preserve">பந்து </t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2242,12 +2242,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
         <is>
           <t xml:space="preserve">சிலந்தி </t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2275,12 +2275,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
         <is>
           <t xml:space="preserve">ம் </t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2308,12 +2308,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
         <is>
           <t xml:space="preserve">தும்பி    </t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2341,12 +2341,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
         <is>
           <t xml:space="preserve">மேகம்  </t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2374,12 +2374,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
         <is>
           <t xml:space="preserve">ன்  </t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2407,12 +2407,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
         <is>
           <t xml:space="preserve">பன்றி    </t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2440,12 +2440,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
         <is>
           <t xml:space="preserve">காளான்    </t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2473,12 +2473,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
         <is>
           <t xml:space="preserve">மீன்   </t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2506,12 +2506,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
         <is>
           <t xml:space="preserve">ய் </t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2539,12 +2539,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
         <is>
           <t xml:space="preserve">அம்பு   </t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2572,12 +2572,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
         <is>
           <t xml:space="preserve">நாய்  </t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2605,12 +2605,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
         <is>
           <t xml:space="preserve">ர்  </t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2638,12 +2638,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
         <is>
           <t xml:space="preserve">ஏர்  </t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2671,12 +2671,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
         <is>
           <t xml:space="preserve">வேர்  </t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2704,12 +2704,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
         <is>
           <t xml:space="preserve">ல்  </t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2737,12 +2737,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
         <is>
           <t xml:space="preserve">முயல்  </t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2770,12 +2770,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
         <is>
           <t xml:space="preserve">அணில்  </t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2803,12 +2803,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
         <is>
           <t xml:space="preserve">வ்     </t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2836,12 +2836,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
         <is>
           <t xml:space="preserve">செவ்வானம்   </t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2869,12 +2869,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
         <is>
           <t xml:space="preserve">செவ்வந்தி </t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2902,12 +2902,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
         <is>
           <t xml:space="preserve">மிளகாய்  </t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2935,12 +2935,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
         <is>
           <t xml:space="preserve">ழ் </t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2968,12 +2968,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
         <is>
           <t xml:space="preserve">தாழ்ப்பாள்  </t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3001,12 +3001,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
         <is>
           <t xml:space="preserve">யாழ் </t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3034,12 +3034,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
         <is>
           <t xml:space="preserve">ள் </t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3067,12 +3067,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
         <is>
           <t xml:space="preserve">முள் </t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3100,12 +3100,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
         <is>
           <t xml:space="preserve">தேள் </t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3133,12 +3133,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
         <is>
           <t xml:space="preserve">க்  </t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3166,12 +3166,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
         <is>
           <t xml:space="preserve">ச் </t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3199,12 +3199,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
         <is>
           <t xml:space="preserve">ண் </t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3232,12 +3232,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
         <is>
           <t xml:space="preserve">ஞ் </t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3265,12 +3265,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
         <is>
           <t xml:space="preserve">த் </t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3298,12 +3298,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
         <is>
           <t xml:space="preserve">ந் </t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3331,12 +3331,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
         <is>
           <t xml:space="preserve">ப்  </t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3364,12 +3364,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
         <is>
           <t xml:space="preserve">ம் </t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3397,12 +3397,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
         <is>
           <t xml:space="preserve">அந்திமல்லி பூத்திருக்கு </t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3430,12 +3430,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
         <is>
           <t xml:space="preserve">ஆலமரம் காத்திருக்கு </t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3463,12 +3463,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
         <is>
           <t xml:space="preserve">இலவம்பஞ்சு வெடிச்சிருக்கு </t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3496,12 +3496,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
         <is>
           <t xml:space="preserve">ங்  </t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3529,12 +3529,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
         <is>
           <t xml:space="preserve">ஒன்று இரண்டு கத்துக்குவோம் </t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3562,12 +3562,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
         <is>
           <t xml:space="preserve">அகல்  </t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3595,12 +3595,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
         <is>
           <t xml:space="preserve">ஓடி ஆடிப் பாடிடுவோம் </t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3628,12 +3628,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
         <is>
           <t xml:space="preserve">ஔவை மொழியை அறிந்திடுவோம் </t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3661,12 +3661,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
         <is>
           <t xml:space="preserve">ஊஞ்சல் </t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3694,12 +3694,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
         <is>
           <t xml:space="preserve">பல் </t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3727,12 +3727,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
         <is>
           <t xml:space="preserve">பணம் </t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3760,12 +3760,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
         <is>
           <t xml:space="preserve">ஓடம் </t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3793,12 +3793,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
         <is>
           <t xml:space="preserve">ஊதல் </t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3826,12 +3826,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
         <is>
           <t xml:space="preserve">நகம் </t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3859,12 +3859,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
         <is>
           <t xml:space="preserve">வட்டம் </t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3892,12 +3892,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
         <is>
           <t xml:space="preserve">வயல் </t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3925,12 +3925,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
         <is>
           <t xml:space="preserve">பழங்கள் </t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3958,12 +3958,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
         <is>
           <t xml:space="preserve">மத்தளம்  </t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3991,12 +3991,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
         <is>
           <t xml:space="preserve">ஏற்றம்  </t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4024,12 +4024,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
         <is>
           <t xml:space="preserve">கட்டம் சட்டம் மட்டம் </t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4057,12 +4057,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
         <is>
           <t xml:space="preserve">மலர் பழம் வனம் </t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4090,12 +4090,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
         <is>
           <t xml:space="preserve">மத்தளம் அப்பளம் </t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4123,12 +4123,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
         <is>
           <t xml:space="preserve">கண் மண் </t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4156,12 +4156,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
         <is>
           <t xml:space="preserve">மணல் சணல் </t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4189,12 +4189,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
         <is>
           <t xml:space="preserve">காகம் </t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4222,12 +4222,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
         <is>
           <t xml:space="preserve">ஓணான் </t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4255,12 +4255,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
         <is>
           <t xml:space="preserve">தாத்தா </t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4288,12 +4288,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
         <is>
           <t xml:space="preserve">நாய் </t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4321,12 +4321,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
         <is>
           <t xml:space="preserve">பாய் </t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4354,12 +4354,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
         <is>
           <t xml:space="preserve">பலா     </t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4387,12 +4387,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
         <is>
           <t xml:space="preserve">வாள் </t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4420,12 +4420,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
         <is>
           <t xml:space="preserve">காளான் </t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4453,12 +4453,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
         <is>
           <t xml:space="preserve">கிண்ணம் </t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4486,12 +4486,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
         <is>
           <t xml:space="preserve">சிங்கம் </t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4519,12 +4519,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
         <is>
           <t xml:space="preserve">கரடி </t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4552,12 +4552,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
         <is>
           <t xml:space="preserve">சிப்பி </t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4585,12 +4585,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
         <is>
           <t xml:space="preserve">அணில் </t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4618,12 +4618,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
         <is>
           <t xml:space="preserve">கத்தி </t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4651,12 +4651,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
         <is>
           <t xml:space="preserve">நிலா </t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4684,12 +4684,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
         <is>
           <t xml:space="preserve">நரி </t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4717,12 +4717,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
         <is>
           <t xml:space="preserve">மயில் </t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4750,12 +4750,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
         <is>
           <t xml:space="preserve">அகழி         </t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4783,12 +4783,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
         <is>
           <t xml:space="preserve">எலி </t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4816,12 +4816,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
         <is>
           <t xml:space="preserve">வில் </t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4849,12 +4849,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
         <is>
           <t xml:space="preserve">கிளி     </t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4882,12 +4882,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
         <is>
           <t xml:space="preserve">பன்றி </t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4915,12 +4915,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
         <is>
           <t xml:space="preserve">இடி படி நடி </t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4948,12 +4948,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
         <is>
           <t xml:space="preserve">மணி ஆணி ஏணி </t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4981,12 +4981,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
         <is>
           <t xml:space="preserve">அல்லி பல்லி </t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5014,12 +5014,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
         <is>
           <t xml:space="preserve">பின்னல் மின்னல் </t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5047,12 +5047,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
         <is>
           <t xml:space="preserve">கண்ணாடி கிண்ணம் </t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5080,12 +5080,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
         <is>
           <t xml:space="preserve">கீரி </t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5113,12 +5113,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
         <is>
           <t xml:space="preserve">சீரகம் </t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5146,12 +5146,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
         <is>
           <t xml:space="preserve">தீ </t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5179,12 +5179,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
         <is>
           <t xml:space="preserve">பீரங்கி </t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5212,12 +5212,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
         <is>
           <t xml:space="preserve">நீச்சல் </t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5245,12 +5245,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
         <is>
           <t>மீன்  விண்மீன்</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5278,12 +5278,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
         <is>
           <t xml:space="preserve">அட ! இளநீர் </t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5311,12 +5311,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
         <is>
           <t xml:space="preserve">ம்ம்ம்... </t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5344,12 +5344,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
         <is>
           <t xml:space="preserve">மேகக் கூட்டங்கள் !  </t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5377,12 +5377,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
         <is>
           <t xml:space="preserve">மின்னுது பார் தூரத்திலே  </t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5410,12 +5410,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
         <is>
           <t xml:space="preserve">மின்னல் கீற்றுகள் ! </t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5443,12 +5443,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
         <is>
           <t xml:space="preserve">தாளம் தப்பாமல்  </t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5476,12 +5476,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
         <is>
           <t xml:space="preserve">வெளியில் நிற்காமல் ! </t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5509,12 +5509,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
         <is>
           <t xml:space="preserve">கள்ளம் இல்லாமல் !  </t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5542,12 +5542,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
         <is>
           <t xml:space="preserve">தடதட என இடி இடிக்குது  </t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5575,12 +5575,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
         <is>
           <t xml:space="preserve">கப்பல் விட்டு மகிழ்வோமே  </t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5608,12 +5608,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
         <is>
           <t xml:space="preserve">குடுகுடு என ஓடுவோமே </t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5641,12 +5641,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
         <is>
           <t xml:space="preserve">கலகல எனச் சிரிப்போமே  </t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5674,12 +5674,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
         <is>
           <t xml:space="preserve">கூடு </t>
         </is>
       </c>
-      <c r="G152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5707,12 +5707,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
         <is>
           <t xml:space="preserve">மூடி </t>
         </is>
       </c>
-      <c r="G153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5740,12 +5740,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
         <is>
           <t xml:space="preserve">கூண்டு </t>
         </is>
       </c>
-      <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5773,12 +5773,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr">
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
         <is>
           <t xml:space="preserve">பூரான் </t>
         </is>
       </c>
-      <c r="G155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5806,12 +5806,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr">
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
         <is>
           <t xml:space="preserve">கல்லூரி </t>
         </is>
       </c>
-      <c r="G156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5839,12 +5839,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr">
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
         <is>
           <t xml:space="preserve">வல்லூறு </t>
         </is>
       </c>
-      <c r="G157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5872,12 +5872,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
         <is>
           <t xml:space="preserve">பூங்கா </t>
         </is>
       </c>
-      <c r="G158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5905,12 +5905,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
         <is>
           <t xml:space="preserve">தூண் </t>
         </is>
       </c>
-      <c r="G159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5938,12 +5938,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr">
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
         <is>
           <t xml:space="preserve">தூண்டில் </t>
         </is>
       </c>
-      <c r="G160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5971,12 +5971,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
         <is>
           <t xml:space="preserve">குண்டூசி </t>
         </is>
       </c>
-      <c r="G161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6004,12 +6004,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr">
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
         <is>
           <t xml:space="preserve">ஒன்று </t>
         </is>
       </c>
-      <c r="G162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6037,12 +6037,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr">
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
         <is>
           <t xml:space="preserve">நூல்கண்டு </t>
         </is>
       </c>
-      <c r="G163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6070,12 +6070,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
         <is>
           <t xml:space="preserve"> இரண்டு </t>
         </is>
       </c>
-      <c r="G164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6103,12 +6103,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
         <is>
           <t xml:space="preserve"> நான்கு  </t>
         </is>
       </c>
-      <c r="G165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6136,12 +6136,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr">
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
         <is>
           <t xml:space="preserve"> ஐந்து </t>
         </is>
       </c>
-      <c r="G166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6169,12 +6169,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
         <is>
           <t xml:space="preserve"> ஆறு </t>
         </is>
       </c>
-      <c r="G167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6202,12 +6202,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr">
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
         <is>
           <t xml:space="preserve"> மூன்று  </t>
         </is>
       </c>
-      <c r="G168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6235,12 +6235,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr">
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
         <is>
           <t xml:space="preserve"> எட்டு  </t>
         </is>
       </c>
-      <c r="G169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6268,12 +6268,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr">
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
         <is>
           <t xml:space="preserve"> ஏழு </t>
         </is>
       </c>
-      <c r="G170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6301,12 +6301,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
         <is>
           <t xml:space="preserve"> பத்து </t>
         </is>
       </c>
-      <c r="G171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6334,12 +6334,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr">
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
         <is>
           <t xml:space="preserve">அச்சுவெல்லம் தின்று பார்த்து இனிப்புச் சுவையைக் கண்டுபிடி </t>
         </is>
       </c>
-      <c r="G172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6367,12 +6367,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr">
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
         <is>
           <t xml:space="preserve"> ஒன்பது </t>
         </is>
       </c>
-      <c r="G173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6400,12 +6400,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
         <is>
           <t xml:space="preserve">வேப்ப இலையை மென்று பார்த்து,கசப்புச் சுவையைக் கண்டுபிடி </t>
         </is>
       </c>
-      <c r="G174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6433,12 +6433,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
         <is>
           <t xml:space="preserve">இனிப்பு </t>
         </is>
       </c>
-      <c r="G175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6466,12 +6466,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr">
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
         <is>
           <t xml:space="preserve">உவர்ப்பு </t>
         </is>
       </c>
-      <c r="G176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6499,12 +6499,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr">
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
         <is>
           <t xml:space="preserve">கசப்பு </t>
         </is>
       </c>
-      <c r="G177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6532,12 +6532,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr">
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
         <is>
           <t>நான் ஊஞ்சலை விட்டு  இறங்கப் போகிறேன்.அவர்கள் ஆடட்டும்</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6565,12 +6565,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr">
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
         <is>
           <t>நீர் வீணாவதைத் தடுத்தாய்.  நன்றி</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6598,12 +6598,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr">
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
         <is>
           <t>வியப்பாக இருக்கிறது.  இங்கு எல்லாமே பேசுகிறதே!</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6631,12 +6631,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
         <is>
           <t>மல்லி எழுந்திரு.  பூங்காவிற்குச் செல்ல வேண்டுமே!</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6664,12 +6664,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr">
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
         <is>
           <t>நான் ஊஞ்சலை விட்டு  இறங்கப் போகிறேன்.அவர்கள் ஆடட்டும்</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6697,12 +6697,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr">
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
         <is>
           <t xml:space="preserve">என் பெயர் எழில். </t>
         </is>
       </c>
-      <c r="G183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6730,12 +6730,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr">
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
         <is>
           <t xml:space="preserve"> அம்மா எதையும் பொறுமையுடன் கேட்பார். எதையும் முதலில்  அம்மாவிடம்தான் சொல்வேன்</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6763,12 +6763,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr">
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
         <is>
           <t xml:space="preserve">அடுத்த நாள். . . </t>
         </is>
       </c>
-      <c r="G185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6796,12 +6796,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr">
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
         <is>
           <t xml:space="preserve">இனி அவர்கள் எதையும் மறந்துவிட்டுச் செல்லமாட்டார்கள்.நீங்களும் தானே </t>
         </is>
       </c>
-      <c r="G186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6829,12 +6829,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr">
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
         <is>
           <t xml:space="preserve">நேர்த்தியான இறகிது </t>
         </is>
       </c>
-      <c r="G187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6862,12 +6862,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr">
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
         <is>
           <t>நீச்சல் போட்டி என்றாலே எப்போதும் எனக்குத்தான் முதல்  பரிசு. தெரியும் தானே!</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6895,12 +6895,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr">
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
         <is>
           <t xml:space="preserve">அம்மா நாம் எங்கே போகப் போகிறோம்?        </t>
         </is>
       </c>
-      <c r="G189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6928,12 +6928,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr">
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
         <is>
           <t xml:space="preserve">நாங்கள் ஜாங்கிரி எடுத்து வந்துள்ளோம் </t>
         </is>
       </c>
-      <c r="G190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6961,12 +6961,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F191" t="inlineStr">
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
         <is>
           <t xml:space="preserve">ஐ! மயில். அழகாக உள்ளது. அக்கா என்றான் அஜ்மல். </t>
         </is>
       </c>
-      <c r="G191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6994,12 +6994,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F192" t="inlineStr">
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
         <is>
           <t>நம் இருவரையும்  வேலைக்குக் கூப்பிட்டார்</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -7027,12 +7027,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr">
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
         <is>
           <t xml:space="preserve">நான் விடியற்காலையில் எழுந்துவிடுவேன். அதனால் நிறைய நேரம் கிடைத்தது. காலை நேரம் எவ்வளவு அழகு தெரியுமா? </t>
         </is>
       </c>
-      <c r="G193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7060,12 +7060,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr">
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
         <is>
           <t>இதோ இந்தத் தார்ச்சாலை அப்போது இல்லை. மண்சாலைதான் குளம் முழுவதும் நீர் நிரம்பி இருக்கும். மாடு, குதிரை போன்றவை தண்ணீர் குடிக்க வந்து போகும். காகம் குளத்தில் குளிக்கும். மீன் துள்ளிக் குதிக்கும். வாத்து கூட்டம் கூட்டமாய் நீந்துவதைப் பார்க்க அழகாக இருக்கும். மீன் பிடிக்க கொக்கு  நிற்கும். குளத்தின் அருகே பெரிய மரம் இருக்கும். அங்கு குருவி கீச்சிடும். அதன் பழங்களைக் கொத்தித் தின்ன கிளி பறந்துவரும் இவற்றை எல்லாம் பார்க்க எவ்வாவு அழகாக இருக்கும் தெரியுமா?.</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -7093,12 +7093,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr">
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
         <is>
           <t xml:space="preserve">  இது விலைமதிப்பு மிக்கது.</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -7126,12 +7126,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr">
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
         <is>
           <t xml:space="preserve"> புல் வகையைச் சார்ந்தது.</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -7159,12 +7159,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr">
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
         <is>
           <t xml:space="preserve"> மிகவேகமாக வளரக்கூடியது.</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -7192,12 +7192,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr">
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
         <is>
           <t xml:space="preserve"> தாவரங்கள், விலங்குளிடமிருந்து கிடைக்கிறது.</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -7225,12 +7225,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr">
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
         <is>
           <t xml:space="preserve"> செயற்கையாகவும் தயாரிக்கப்படுகிறது.</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7258,12 +7258,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr">
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
         <is>
           <t xml:space="preserve"> மிட்டாய்கள், மருந்துப் பொருள்கள் செய்யவும் பயன்படுகிறது.</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -7291,12 +7291,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F201" t="inlineStr">
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
         <is>
           <t xml:space="preserve"> மரப்பொந்துகளில் கூடுகட்டும்.</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -7324,12 +7324,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr">
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
         <is>
           <t xml:space="preserve"> இதன் காம்பு நீண்டு இருக்கும்.</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7357,12 +7357,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F203" t="inlineStr">
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
         <is>
           <t xml:space="preserve">க்,ச்,ட்த்,ப்,ற் </t>
         </is>
       </c>
-      <c r="G203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7390,12 +7390,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr">
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
         <is>
           <t>அது போலய்,ர்,ல்,வ்,ழ்,ள் - என்ற எழுத்துகளும், வன்மையாகவும் இல்லாமல் மென்மையாகவும் இல்லாமல் இடைப்பட்ட ஓசை உடையதால் இவற்றுக்கு  இடையினம் என்று பெயரிடுவோம்.</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7423,12 +7423,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F205" t="inlineStr">
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
         <is>
           <t xml:space="preserve">தோண்டுகின்ற பொழுதெல்லாம் ஊற்றைப்போல் சுரக்கின்ற </t>
         </is>
       </c>
-      <c r="G205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7456,12 +7456,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F206" t="inlineStr">
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
         <is>
           <t xml:space="preserve">பாடல் பொருள் </t>
         </is>
       </c>
-      <c r="G206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7489,12 +7489,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F207" t="inlineStr">
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
         <is>
           <t>அறிந்த தகவல்களையும், செய்திகளையும் சரியான ஒலிப்புடன் தங்கு தடையின்றிக் கலவைத் தொடரில்  பேசுதல்...என்ன செய்வது என்று தெரியாமல் ஐயோ காப்பாற்றுங்கள்” காப்பாற்றுங்கள் என்று 108 உரக்கக் கத்தினான், உடனே அந்தப் பெரியவர் தன் பையிலிருந்து செல்பேசியை எடுத்தார்.</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7522,12 +7522,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr">
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr">
         <is>
           <t>அதன்பிறகு பள்ளிக்குச் சென்றான். ஆசிரியர் கண்ணனைப் பார்த்து ஏன் தாமதமாக வருகிறாய்? எனக் கேட்டார்.  கண்ணன் நடந்தவற்றைத் தெளிவாகக் கூறினான். ஆசிரியர் அவனைப் பாராட்டினார். கண்ணன் மகிழ்ச்சியடைந்தான்.</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7555,12 +7555,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr">
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr">
         <is>
           <t xml:space="preserve">யானை மேலே ஊர்கோலமாம்  </t>
         </is>
       </c>
-      <c r="G209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7588,12 +7588,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr">
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr">
         <is>
           <t xml:space="preserve">பூனைக்கும் பூனைக்கும் கல்யாணமாம்  </t>
         </is>
       </c>
-      <c r="G210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7621,12 +7621,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr">
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
         <is>
           <t xml:space="preserve">ஒட்டகச்சிவிங்கி நாட்டியமாம்  </t>
         </is>
       </c>
-      <c r="G211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7654,12 +7654,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr">
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr">
         <is>
           <t xml:space="preserve">கொர்கொர் குரங்கு பின்பாட்டாம்  </t>
         </is>
       </c>
-      <c r="G212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7687,12 +7687,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F213" t="inlineStr">
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr">
         <is>
           <t xml:space="preserve">பூலோகமெல்லாம் கொண்டாட்டமாம்  </t>
         </is>
       </c>
-      <c r="G213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7720,12 +7720,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F214" t="inlineStr">
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr">
         <is>
           <t>﻿அப்போது மேரியின் வீட்டு மாட்டுத் தொழுவத்தில் ஒரே கும்பல்.....ஓடிச்சென்று  பார்த்தனர் அவர்கள் கண்ட காட்சி கல்நெஞ்சையும் கசிந்துருகச் செய்வதாக இருந்தது.... கன்றை ஈன்ற பசு தனது கழிவினை வெளியே தள்ள முடியாமல் இறந்துபோயிருந்தது. பாதி வெளிவந்திருந்த கழிவில் நிறைய நெகிழிக் குப்பைகள் காணப்பட்டன. அந்நெகிழியால் தான் இறப்பு ஏற்பட்டதாகக் கால்நடை மருத்துவர்  கூறிக் கொண்டிருந்தார்.</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7753,12 +7753,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr">
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr">
         <is>
           <t>﻿பள்ளி மாணவர்கள், ஆசிரியர்கள், பள்ளி மேலாண்மைக் குழு உறுப்பினர்கள்,ஊர்ப் பொதுமக்கள் ஆகியோரைக் கொண்டு நெகிழி விழிப்புணர்வு பேரணி நடத்தத்  தீர்மானம் நிறைவேற்றப்பட்டது. அனைவரும் விழிப்புணர்வு வாசகங்கள் எழுதப்பட்ட பதாகைகளை ஏந்தி வாசகங்களைக் கூறிக் கொண்டே கிராமத்தின் அனைத்துத் தெருக்களிலும் பேரணியாக வந்தனர்.</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7786,12 +7786,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr">
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr">
         <is>
           <t xml:space="preserve">நாம் விதைக்கும் விதைகளில் முயற்சியுடன் மண்ணைப் பிளந்து கொண்டு வருபவையே செடிகளாகின்றன. தயங்கி நிற்பவை தங்கி விடுகின்றன. அதுபோல கவியரசி தயங்காமல் துணிச்சலாகச் செயல்பட்டதால் வெற்றி பெற்றாள் எனக் ஆசிரியை கூறினார். </t>
         </is>
       </c>
-      <c r="G216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7819,12 +7819,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr">
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr">
         <is>
           <t xml:space="preserve">கற்றவர்களின் முன் தான் கற்ற கல்வியைக் கூறுதல் இனிமையானது.அறிவில் மேம்பட்டவர்களுடன் சேர்ந்திருப்பது மிகவும் இனிமையானது. </t>
         </is>
       </c>
-      <c r="G217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7852,12 +7852,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F218" t="inlineStr">
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr">
         <is>
           <t xml:space="preserve">தேனருவி: மாமா இங்கு என்னென்ன நூல்கள் இருக்கும்? </t>
         </is>
       </c>
-      <c r="G218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7885,12 +7885,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr">
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr">
         <is>
           <t>தேனருவி: நான் வழக்கமாகப் பள்ளிக்கூடம் போகும் வழியில் உள்ள ஒரு  கட்டடத்தைத் தோரணம் கட்டி அழகுபடுத்தியிருந்தார்கள். அதில் நூலகம் என்று எழுதியிருக்கு அப்படின்னா..... என்ன மாமா....?.</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7918,12 +7918,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F220" t="inlineStr">
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr">
         <is>
           <t>மாமா:ம். என் செல்லக் குட்டி கேட்டால் சொல்லாமல் இருப்பேனா? இங்கு வந்து நமக்குத் தேவையான அல்லது பிடித்த நூல்களை எடுத்துப் படிக்கலாம். நூலகத்தில் உறுப்பினராகச் சேர்ந்தால் நூல்களை வீட்டிற்கே கொண்டு சென்றும் படிக்கலாம்  ஆனால் குறிப்பிட்ட நாளில் மீண்டும் புத்தகங்களைத் திருப்பி அளித்து விடவேண்டும். இதனால்,</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -7951,12 +7951,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr">
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr">
         <is>
           <t>நூலகத்தில் உள்ள  வாசகர் வட்டம் மூலமாக நூலக தினத்தன்று குழந்தைகளுக்கான போட்டிகள் அனைத்து நூலகங்களிலும் நடத்தப்படுகின்றன.</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -7984,12 +7984,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F222" t="inlineStr">
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr">
         <is>
           <t xml:space="preserve">பாடினது போதும், ஏதாவது கதை சொல்லுங்க தாத்தா என்றனர் பிள்ளைகள். </t>
         </is>
       </c>
-      <c r="G222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -8017,12 +8017,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr">
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr">
         <is>
           <t xml:space="preserve">இளமதி: ம்………யோசித்துவிட்டு, 'தெரியலை' தாத்தா </t>
         </is>
       </c>
-      <c r="G223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8050,12 +8050,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr">
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr">
         <is>
           <t xml:space="preserve">தாத்தா :யோசிங்க…. யோசிங்க….. நல்லா யோசிங்க ஓரெழுத்து உறுப்பு எது? இளமதி நீ சொல்லு </t>
         </is>
       </c>
-      <c r="G224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -8083,12 +8083,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr">
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr">
         <is>
           <t xml:space="preserve"> தாத்தா :மூன்றாம் எழுத்து உடலின் உறுப்பு, முதலும் மூன்றும் நட்புக்கு எதிரி, ஒன்றும் இரண்டும் நிறைய தரும், மூன்றும் சேர்ந்தால் உட்கார உதவும் அது என்ன?</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -8116,12 +8116,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr">
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr">
         <is>
           <t xml:space="preserve">தாத்தா: நல்லது மிகச்சரியான பதில், இப்ப இளமதியைக் கேட்கிறேன்... ஆறையும் ஐந்தையும் கூட்டினால் பணம் வராது…..ஆனா பழம் வரும் அது என்ன?  </t>
         </is>
       </c>
-      <c r="G226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -8149,12 +8149,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F227" t="inlineStr">
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr">
         <is>
           <t xml:space="preserve">இளமதி :பேச்சை மாத்தாதீங்க தாத்தா பதிலைச் சொல்லுங்க. சீக்கிரம்….  </t>
         </is>
       </c>
-      <c r="G227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -8182,12 +8182,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F228" t="inlineStr">
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr">
         <is>
           <t xml:space="preserve">மணவாளன் :சரி தாத்தா ……இப்ப நாங்க கேட்கிறோம் .... நீங்க சொல்லுங்க, பிறக்கும்போது நிறமும் சுவையும் இல்லாத சுந்தரன் ஊருக்கு ஊர் நிறம் மாறிச் சுவை மாறுவான் அவன் யார்?.  </t>
         </is>
       </c>
-      <c r="G228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -8215,12 +8215,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr">
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr">
         <is>
           <t xml:space="preserve">இளமதி :தாத்தா, அத்தை வீடு வந்துவிட்டது.  </t>
         </is>
       </c>
-      <c r="G229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -8248,12 +8248,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F230" t="inlineStr">
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr">
         <is>
           <t xml:space="preserve">  தாத்தா :ம்ம்ம்.... எல்லாரோட தாகத்தையும் தீர்க்கும் தண்ணீர் தானே</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -8281,12 +8281,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F231" t="inlineStr">
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr">
         <is>
           <t xml:space="preserve">  அனைவரும் வண்டியைவிட்டு இறங்கி, ஆவலுடன் வீட்டை நோக்கிச் சென்றனர்</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -8314,12 +8314,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr">
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr">
         <is>
           <t xml:space="preserve">  தாத்தா :சரி, சற்றுப் பொறுங்கள் வண்டியை ஓரமாக நிறுத்துகிறேன்.  </t>
         </is>
       </c>
-      <c r="G232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -8347,12 +8347,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr">
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr">
         <is>
           <t xml:space="preserve">என்றுமில்லைவெற்றியே! </t>
         </is>
       </c>
-      <c r="G233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -8380,12 +8380,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr">
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr">
         <is>
           <t xml:space="preserve">அதனால், உப்பு கரைந்து எடை குறைந்தது. எடை குறைவதை அறிந்துகொண்ட கழுதை, நாள்தோறும் ஓடைநீரில் மூட்டைகளை அசைத்துத் தள்ளியது. கழுதையின் ஏமாற்று வேலையைப் புரிந்துகொண்ட உரிமையாளர், அதற்குப் பாடம் புகட்ட எண்ணினார். மற்றொரு நாள் உரிமையாளர், கழுதையின் முதுகில் பஞ்சுமூட்டைகளை ஏற்றிக்கொண்டு ஓடை வழியே சென்றார். </t>
         </is>
       </c>
-      <c r="G234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -8413,12 +8413,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr">
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr">
         <is>
           <t>பஞ்சாயத்துத் தலைவர் கூட்டத்திற்கு வந்திருந்தவர்களை வரவேற்றுப் பேசினார். அரசின் சிறுதொழில் தொடங்குவதற்கான உதவித்தொகை வழங்கும் திட்டம் குறித்துப்பேசினார். இத்திட்டத்தின்கீழ் யார் யாருக்கெல்லாம் உதவித்தொகை  வந்திருக்கிறதோ அவர்களின் பெயர்களைப் படித்தார்.</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -8446,12 +8446,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr">
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr">
         <is>
           <t xml:space="preserve">பொன்வண்ணன் சற்றுக் குற்ற உணர்வோடு தலை குனிந்தபடி கூறினார், “ஐயா! நான் மிதிவண்டி பழுதுபார்க்கும் கடை வைத்திருக்கிறேன். </t>
         </is>
       </c>
-      <c r="G236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8479,12 +8479,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F237" t="inlineStr">
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr">
         <is>
           <t>உங்கள் அறியாமையால் இப்போது என்னவாயிற்று பார்த்தீர்களா? அரசின் உதவித் தொகையை உங்களால் பெற முடியாமல் போய்விட்டதே. கல்வி அறிவு  இருந்தால்தான் நாள்தோறும் நம்மைச் சுற்றி நடக்கும் நிகழ்ச்சிகளையும் அறிவியல் மாற்றங்களையும் அறிந்து கொள்ள முடியும். நம்மையும் மேம்படுத்திக் கொள்ள முடியும்.</t>
         </is>
       </c>
-      <c r="G237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8512,12 +8512,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr">
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr">
         <is>
           <t xml:space="preserve">கல்வி, தொழிலுக்கு வழிகாட்டுகிறது. வாழ்க்கையை நெறிப்படுத்த உதவுகிறது. இப்போதாவது புரிந்து கொண்டீர்களா? </t>
         </is>
       </c>
-      <c r="G238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -8545,12 +8545,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr">
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr">
         <is>
           <t xml:space="preserve"> “ஐயா! இப்ப நான் நன்கு புரிந்து கொண்டேன். நான்தான் கல்வி கற்காமல் இருந்து விட்டேன். என் மகனாவது நன்கு படித்து வாழ்வில் முன்னேறட்டும். </t>
         </is>
       </c>
-      <c r="G239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -8578,12 +8578,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F240" t="inlineStr">
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr">
         <is>
           <t xml:space="preserve">﻿இனி நான் என் மகனை வேலைக்காகப் பள்ளியைவிட்டு நிறுத்த மாட்டேன். இப்போதே என் மகனை அழைத்துச் சென்று தலைமை ஆசிரியரிடம் மீண்டும் பள்ளியில்  சேர்த்துக்கொள்ளுமாறு நான் வேண்டிக்கொள்வேன். </t>
         </is>
       </c>
-      <c r="G240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -8611,12 +8611,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr">
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr">
         <is>
           <t xml:space="preserve">சித்தப்பா பரிசலில் செல்லும் வழியில் என்னென்ன பார்த்தீர்கள்? </t>
         </is>
       </c>
-      <c r="G241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -8644,12 +8644,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F242" t="inlineStr">
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr">
         <is>
           <t xml:space="preserve">அங்கவை: ஒகேனக்கல் என்பதற்குப் புகையும் கல்பாறை எனப்பொருள். கன்னடத்தில் ஒகே என்பது புகை ஆகும். அருவிநீர் கல்பாறையில் பட்டுத் தெறித்து, வெண்புகை போலத் தோற்றம் அளிப்பதால் தான் இப்பெயர் வந்தது. காவேரி ஆறு கர்நாடகத்திலுள்ள குடகுமலையில் தோன்றி இங்குதான் தமிழ்நாட்டு எல்லைக்குள் நுழைகிறது </t>
         </is>
       </c>
-      <c r="G242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -8677,12 +8677,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F243" t="inlineStr">
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr">
         <is>
           <t xml:space="preserve">அந்த நாயைத் தின்று விடலாமா என்று ஓநாய் நினைத்தது. ஆனால், தான் அப்போது இருந்த சோர்வான நிலையில் அந்த நாயுடன் சண்டை போட்டுத் தோற்கடிக்க  முடியுமா?என்பது சந்தேகமாய் இருந்தது. </t>
         </is>
       </c>
-      <c r="G243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -8710,12 +8710,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F244" t="inlineStr">
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr">
         <is>
           <t xml:space="preserve">முயலிடம் தொடர்ந்து நீ நட்பு வைத்துக்கொண்டால் உன்னை ஏதாவது ஆபத்தில் மாட்டிவிடும்" என்றது நரி. மானிற்கு நரியின் தந்திரம் புரியவில்லை. அது எப்படி? என்று கேட்டது. அதற்கு நரியானது, அதோ தூரத்தில் தெரிகிற குகைக்கு முயல் உன்னை அழைத்துச் சென்று அங்கு வாழும் சிங்கத்திற்கு இரையாக்கிவிடும் என்று பொய் கூறியது. </t>
         </is>
       </c>
-      <c r="G244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -8743,12 +8743,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F245" t="inlineStr">
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr">
         <is>
           <t xml:space="preserve">அடர்ந்த காட்டில் முயலும் மானும் நெடுநாள் நண்பர்களாக வாழ்ந்து வந்தன.இரண்டு விலங்குகளும் அன்பாய்ப் பழகி வந்தன. மான் பார்ப்பதற்கு அழகாக இருந்ததால் எப்படியாவது வேட்டையாடி விடவேண்டும் என்ற எண்ணம் அங்குள்ள நரிக்குத் தோன்றியது. நரி ஒரு நாள் மானிடம் "நண்பனே! நீ உன் நண்பன் முயல்மீது அளவுக்கு மீறிய பாசம் வைத்துள்ளாய்! என்பதை நான் அறிவேன். </t>
         </is>
       </c>
-      <c r="G245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -8776,12 +8776,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F246" t="inlineStr">
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr">
         <is>
           <t xml:space="preserve"> நரியும் வேறுவழியில்லாமல் மானை விடுவித்தது. மான் மகிழ்ச்சியுடன் முயலுடன் ஒன்று சேர்ந்து வாழ்ந்தது.</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -8809,12 +8809,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F247" t="inlineStr">
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr">
         <is>
           <t xml:space="preserve">மூன்றாவதற்கு மெழுகுவத்தி என்பதே விடையாகும் என்றது. முயல் விடை கூறியதைப் பார்த்துத் திகைத்து போனது நரி. நீ கூறியபடி புதிருக்கு விடை சொல்லிவிட்டேன் என் நண்பனை என்னிடம் அனுப்பி விடு' என்று கேட்டது முயல், </t>
         </is>
       </c>
-      <c r="G247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -8842,12 +8842,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F248" t="inlineStr">
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr">
         <is>
           <t>ஆற்றில் நீர் வற்றியதால், அதன் வறண்ட மணல்பகுதி, வெப்பத்தால் சூடேறி நடப்பவரின் பாதங்களைச் சுடும். அத்தகைய நிலையிலும் அந்த ஆற்று மணலைத் தோண்டுகின்ற போது, சுரக்கின்ற ஊற்றானது, உலக மக்களுக்கு உணவாய் அமையும், அதுபோல, உயர்ந்த குடிப்பிறப்பில் தோன்றியவர்கள், வறுமைநிலையில்  வாடினாலும், தம்மிடம் வந்து பொருள் தருக எனக் கேட்பவர்க்கு இல்லை எனக் கூறாது, தம்மால் முடிந்தவரை கொடுத்து உதவுவார்கள்.</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -8875,12 +8875,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F249" t="inlineStr">
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr">
         <is>
           <t xml:space="preserve">தூக்கணாங்குருவியும் ஒட்டகச்சிவிங்கியும் </t>
         </is>
       </c>
-      <c r="G249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -8908,12 +8908,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F250" t="inlineStr">
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr">
         <is>
           <t xml:space="preserve">கணினி நமக்குத் தகவல்களை உடனடியாகத் தருவதால் மன மகிழ்வு ஏற்படுகிறது. இணையத்தின் மூலமாக நல்ல நட்பை உருவாக்குகிறது. கடிதப் போக்குவரத்தை விரைந்து செயல்படுத்துகிறது. கணினி, சிறந்த தகவல் களஞ்சியமாகச் செயல்படுகிறது. </t>
         </is>
       </c>
-      <c r="G250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -8941,12 +8941,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr">
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr">
         <is>
           <t xml:space="preserve">ஒட்டகச்சிவிங்கி: அப்பாடா... என்ன வெயில்... என்ன வெயில் இந்த மரத்தின் அடியில் கொஞ்ச நேரம் ஒதுங்கலாம். என நினைத்தது. </t>
         </is>
       </c>
-      <c r="G251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -8974,12 +8974,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F252" t="inlineStr">
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr">
         <is>
           <t xml:space="preserve">காட்டில் இருந்த பெரிய மரம் ஒன்றின் கிளையில் தன் குஞ்சுகளுடன் கூட்டில் தூக்கணாங்குருவி ஒன்று வசித்து வந்தது. அதன் குஞ்சுகள், கீச் …. கீச் ….என்று ஒலி எழுப்பி மகிழ்ச்சியுடன் இருந்தன. அப்போது அந்த வழியாக ஒட்டகச்சிவிங்கி ஒன்று வந்தது. </t>
         </is>
       </c>
-      <c r="G252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -9007,12 +9007,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F253" t="inlineStr">
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr">
         <is>
           <t xml:space="preserve">தூக்கணாங்குருவி: ஏ ஒட்டகச்சிவிங்கியே! ஏன் மரக்கிளையை உலுக்குகிறாய்? என் கூட்டிலுள்ள குஞ்சுகள் பயப்படுகின்றன. </t>
         </is>
       </c>
-      <c r="G253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -9040,12 +9040,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F254" t="inlineStr">
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr">
         <is>
           <t xml:space="preserve">ஒட்டகச்சிவிங்கி: அப்பாடா! இன்று கொஞ்சம் வெயில் பரவாயிலே. அட, அது என்ன? </t>
         </is>
       </c>
-      <c r="G254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -9073,12 +9073,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F255" t="inlineStr">
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr">
         <is>
           <t xml:space="preserve">நமக்கு ஏற்பட்டதுபோலத்தானே அந்தத் தூக்கணாங்குருவிகளுக்கும் ஏற்பட்டிருக்கும். தங்கள் கூட்டைக் கலைத்ததால்தானே அந்தத் தேனீக்களும் என்னைக் கொட்டின. பாவம், அந்தத் தவளைகள் எத்தனை முறை அவற்றை நான் காலால் மிதித்திருக்கிறேன். </t>
         </is>
       </c>
-      <c r="G255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -9106,12 +9106,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F256" t="inlineStr">
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="inlineStr">
         <is>
           <t xml:space="preserve">உங்கள் குதிரையை சற்றுத் தள்ளி கட்டுங்கள். ஏனெனில், எனது குதிரை முரட்டுத்தனமானது என்றான். அதற்கு வீரன், "முடியாது நான் இங்குத்தான் கட்டுவேன் என்று சொல்லிக் குதிரையைக் கட்டிவிட்டு உணவு உண்ணச் சென்றான். </t>
         </is>
       </c>
-      <c r="G256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -9139,12 +9139,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F257" t="inlineStr">
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr">
         <is>
           <t xml:space="preserve">ஓர் ஊரில் வணிகன் ஒருவன் இருந்தான். அவன் குதிரையில் சென்று வாணிகம் செய்து வந்தான். ஒருநாள் அன்றைய வேலையை முடித்துவிட்டுக் களைப்புடன் வந்த அவன், சற்றுநேரம் ஓய்வு எடுக்க நினைத்தான். தனது குதிரையை அங்கிருந்த மரத்தடியில் கட்டி வைத்து ஓய்வு எடுத்துக் கொண்டிருந்தான் </t>
         </is>
       </c>
-      <c r="G257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -9172,12 +9172,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F258" t="inlineStr">
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr">
         <is>
           <t xml:space="preserve"> வணிகன் கண் அயர்ந்துவிட்டான். வீரன் உணவு உண்ணும் இடைவேளையில் வணிகனின் குதிரை, வீரனின் குதிரையை எட்டி உதைத்துத் தள்ளிவிட்டது. அதனால், வீரனுடைய குதிரையின் கால் உடைந்துவிட்டது. </t>
         </is>
       </c>
-      <c r="G258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -9205,12 +9205,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F259" t="inlineStr">
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr">
         <is>
           <t xml:space="preserve">அதற்கு வீரன் அவன் பேசுவான், ஐயா. அவன்தான் எனது குதிரை முரட்டுத்தனமானது உனது குதிரையை அருகில் கட்டாமல் தூரத்தில் கட்டு எனக் கூறினான். </t>
         </is>
       </c>
-      <c r="G259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -9238,12 +9238,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F260" t="inlineStr">
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr">
         <is>
           <t xml:space="preserve">வீரன் உடனே வணிகனை எழுப்பினான். என் குதிரையின் கால் உன் குதிரையினால் உடைந்துவிட்டதால், எனக்கு நஷ்டஈடு கொடு என்று வணிகனிடம் கேட்டான். அதனை வணிகன் ஏற்றுக் கொள்ளவில்லை. நான் கட்டும்போதே என் குதிரையை முரட்டுக் குதிரை என்றேன். நீ தானே நான் சொன்னதை கேட்காமல் கட்டினாய்? என்று வணிகன் மறுத்துவிட்டான்.  வணிகனே வா! நீதிபதியிடம் செல்லலாம் என்றான் வீரன். இருவரும் நீதிபதியிடம் சென்றனர். </t>
         </is>
       </c>
-      <c r="G260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -9271,12 +9271,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F261" t="inlineStr">
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr">
         <is>
           <t xml:space="preserve">அப்பா : “அட, ஆமா! எங்கேயிருந்து சேற்றைப் பூசிக்கொண்டு வந்ததுன்னு தெரியலேயே?” </t>
         </is>
       </c>
-      <c r="G261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -9304,12 +9304,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F262" t="inlineStr">
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr">
         <is>
           <t xml:space="preserve">அப்பா : “அது சரி, எழிலி, நீயா இருந்தா என்ன செய்வே? </t>
         </is>
       </c>
-      <c r="G262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -9337,12 +9337,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr">
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr">
         <is>
           <t xml:space="preserve">அப்பா : ஏன்னா, நாமெல்லாம் உயர்திணை. விலங்கு, பறவையெல்லாம் அஃறிணை. </t>
         </is>
       </c>
-      <c r="G263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -9370,12 +9370,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F264" t="inlineStr">
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr">
         <is>
           <t xml:space="preserve"> எழிலி : இம். இம்... நீங்க, அம்மா, அண்ணா, அக்கா, தம்பி, சிற்றப்பா, பெரியப்பா, அத்தை அப்புறம்... என்கூட விளையாடுவாங்களே மீனா, ரோசி, கம்ரூன், பாபு, சுரேஷ், கௌதம், சீனு, ராதிகா, ரம்யா, ஐசு, சிருஷ்டி, பாரு, வித்யூன் ....</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -9403,12 +9403,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F265" t="inlineStr">
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr">
         <is>
           <t xml:space="preserve">அப்பா : போதும்.... போதும். உனக்கு நிறைய நண்பர்கள் இருக்காங்கன்னு எனக்குத் தெரியும். உன்னைச் சுற்றி இருக்கிறவங்கன்னு நீ இப்ப சொன்னேல, இவங்க எல்லாருக்கும் உயிரிருக்கு. அதுமட்டுமா? </t>
         </is>
       </c>
-      <c r="G265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -9436,12 +9436,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F266" t="inlineStr">
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr">
         <is>
           <t xml:space="preserve">திணை என்பது, ஒழுக்கம். அதன் அடிப்படையில் உயர்திணை, அஃறிணை என இரண்டாகக் கூறுவர். </t>
         </is>
       </c>
-      <c r="G266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -9469,12 +9469,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F267" t="inlineStr">
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr">
         <is>
           <t xml:space="preserve">அப்பா : அடடே, நீ நல்லாவே யோசிக்கிற எழிலி. ஒவ்வொரு பொருளுக்கும் ஒரு பேரு இருக்குல்லே, அதை வைத்து நீ எளிதாக் கண்டுபிடிக்கலாம். அந்தப் பெயரை வைத்தே அதற்கு உயிரிருக்கா, நம்மைப்போல அது சிந்திக்குமா? வேலை செய்யுமான்னு கண்டுபிடிக்கலாம்ல. பெயரை வைத்தே என்ன திணை, பால், எண், இடம்னு எல்லாத்தையும் கண்டுபிடிக்கலாம். </t>
         </is>
       </c>
-      <c r="G267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -9502,12 +9502,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F268" t="inlineStr">
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr">
         <is>
           <t xml:space="preserve">யாமறிந்த மொழிகளிலே தமிழ்மொழிபோல் இனிதாவது எங்கும் காணோம்’எனத் தமிழைப் போற்றிப் புகழ்கிறார். </t>
         </is>
       </c>
-      <c r="G268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -9535,12 +9535,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F269" t="inlineStr">
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr">
         <is>
           <t xml:space="preserve">'தமிழுக்கு அமுதென்று பேர் - இன்பத்  </t>
         </is>
       </c>
-      <c r="G269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -9568,12 +9568,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F270" t="inlineStr">
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr">
         <is>
           <t xml:space="preserve">தமிழ் எங்கள் உயிருக்கு நேர்'  </t>
         </is>
       </c>
-      <c r="G270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -9601,12 +9601,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F271" t="inlineStr">
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr">
         <is>
           <t xml:space="preserve">எனப் பாரதிதாசனாரும் தமிழின் பெருமையைக் கூறுகிறார். </t>
         </is>
       </c>
-      <c r="G271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -9634,12 +9634,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F272" t="inlineStr">
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr">
         <is>
           <t xml:space="preserve">இயல், இசை, நாடகம் என்னும் மூன்றும் இணைந்தது, முத்தமிழ், இம்மூன்று துறைகளின் கீழ் தமிழ்மொழியின் வெளிப்பாட்டைக் காணலாம். </t>
         </is>
       </c>
-      <c r="G272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -9667,12 +9667,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F273" t="inlineStr">
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr">
         <is>
           <t xml:space="preserve">எழுத்து நடை வாயிலாக வெளிப்படுவது, இயல் பாடல்கள் மூலம் </t>
         </is>
       </c>
-      <c r="G273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -9700,12 +9700,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F274" t="inlineStr">
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr">
         <is>
           <t xml:space="preserve">கணியன் பூங்குன்றனார் எழுதிய 'யாதும் ஊரே, யாவரும் கேளிர்’ என்னும் புறநானூற்றுப்பாடல் தொடர் இன்றளவிலும் ஐக்கிய நாடுகள் அவையில் </t>
         </is>
       </c>
-      <c r="G274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -9733,12 +9733,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F275" t="inlineStr">
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr">
         <is>
           <t>உலகில் உள்ள மொழிகளுள் மிகவும் தொன்மை வாய்ந்தது தமிழ்மொழி.‘அமிழ்தினும் இனிய மொழியாக நம் தமிழ்மொழி விளங்குகிறது. தமிழ், தமிழ் என்று சொல்லிப் பாருங்கள். உங்கள் காதில் 'அமிழ்து, அமிழ்து எனத் தேனாய்ப் பாய்வதை உணர்வீர்கள். அதனால்தான், பாரதியாரும்,  ‘செந்தமிழ் நாடெனும் போதினிலே இன்பத் தேன் வந்து பாயுது காதினிலே என்று பாடியுள்ளார். மேலும்,</t>
         </is>
       </c>
-      <c r="G275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -9766,12 +9766,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F276" t="inlineStr">
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr">
         <is>
           <t>பழங்காலத்தில் தமிழர்கள் பயன்படுத்திய மண்பாண்டங்கள், அணிகலன்கள், பண்பாட்டை வெளிப்படுத்தும் ஆடைகள் ஆகியவற்றை அறிந்துகொள்ள  அகழாய்வுகள் உதவுகின்றன. அண்மையில் சிவகங்கை மாவட்டத்தில் 'கீழடி' என்னுமிடத்தில் நடைபெற்ற அகழாய்வில் தமிழர்களின் பண்பாட்டு அடையாளங்கள் வெளிப்பட்டுள்ளன. இதன் மூலம் தமிழ் மொழி 'ஆதித் தமிழர் மொழி’ என்பது புலப்படுகிறது.</t>
         </is>
       </c>
-      <c r="G276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -9799,12 +9799,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F277" t="inlineStr">
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr">
         <is>
           <t xml:space="preserve">உலக மக்கள் அனைவரும் ஏற்றுக்கொள்ளும் வகையில் சிறப்புப் பெற்று விளங்கும் நூல், திருக்குறள்.’உலகப் பொதுமறை’ என்று அழைக்கப்படும் இந்நூலில், தமிழரின் வாழ்வியல் நெறிகள் காணப்படுகின்றன. </t>
         </is>
       </c>
-      <c r="G277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -9832,12 +9832,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F278" t="inlineStr">
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="inlineStr">
         <is>
           <t xml:space="preserve"> தமிழ்மொழியின் சிறப்பை உணர்ந்த அயல்நாட்டார் பலரும் தமிழைக் கற்றுக் கொண்டதோடு, தமிழில் பல இலக்கண, இலக்கியங்களையும் படைத்துள்ளனர். திருக்குறளின் பெருமையை உலகறியச் செய்தவர், ஜி. யு. போப்.  </t>
         </is>
       </c>
-      <c r="G278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -9865,12 +9865,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F279" t="inlineStr">
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr">
         <is>
           <t>நம் தாய்மொழியான தமிழ், ஈராயிரம் ஆண்டுக்குமேல் பேச்சிலும் எழுத்திலும் பயன்பாட்டில் இருந்து வருகிறது. நாளும் பொலிவுடன் வளர்தமிழாய் தன்  பெருமையை உலக அரங்கில் நிலைநிறுத்தி வருகிறது. ஆகவே, இன்னும் எத்தனையோ ஆண்டுகள் பிறரை வாழ வைக்கவும், வழிநடத்தவும் திறமையுள்ள மொழியாக விளங்கும் நம் தமிழ்மொழியை உலகில் உள்ளோர் பாராட்டும் வகையில் மென்மேலும் உயர்த்த உறுதுணையாக இருப்போம்.</t>
         </is>
       </c>
-      <c r="G279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -9898,12 +9898,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F280" t="inlineStr">
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="inlineStr">
         <is>
           <t xml:space="preserve">அதை எடுத்துப் பார்த்தனர். </t>
         </is>
       </c>
-      <c r="G280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -9931,12 +9931,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F281" t="inlineStr">
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="inlineStr">
         <is>
           <t xml:space="preserve">அதை எடுத்துப் பார்த்தனர். </t>
         </is>
       </c>
-      <c r="G281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -9964,12 +9964,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F282" t="inlineStr">
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr">
         <is>
           <t xml:space="preserve">அதனால் தான் பனைக்குக் “கற்பகத்தரு என்ற பெயரும் உண்டு. </t>
         </is>
       </c>
-      <c r="G282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -9997,12 +9997,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F283" t="inlineStr">
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="inlineStr">
         <is>
           <t xml:space="preserve">தாத்தா: நுங்கும், பனங்கிழங்கும் உணவாகப் பயன்படுகின்றன. </t>
         </is>
       </c>
-      <c r="G283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -10030,12 +10030,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F284" t="inlineStr">
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="inlineStr">
         <is>
           <t xml:space="preserve">மரங்கள் இன்றி மனிதர்கள் இல்லை </t>
         </is>
       </c>
-      <c r="G284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -10063,12 +10063,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F285" t="inlineStr">
+      <c r="F285" t="inlineStr"/>
+      <c r="G285" t="inlineStr">
         <is>
           <t>அதற்கு கிருஷ்ணதேவராயர்  அதிலென்ன சந்தேகம் என்றார்.</t>
         </is>
       </c>
-      <c r="G285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -10096,12 +10096,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F286" t="inlineStr">
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr">
         <is>
           <t xml:space="preserve">இருளாகவும் இருக்கக்கூடாது </t>
         </is>
       </c>
-      <c r="G286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -10129,12 +10129,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F287" t="inlineStr">
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr">
         <is>
           <t xml:space="preserve">தாத்தா: அந்தப் பழமொழிக்குப் பொருள் வேறு அமுதவாணா! கல்லால் செதுக்கிய சிலை தானே கோவில்களில் இருக்கிறது! </t>
         </is>
       </c>
-      <c r="G287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -10162,12 +10162,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F288" t="inlineStr">
+      <c r="F288" t="inlineStr"/>
+      <c r="G288" t="inlineStr">
         <is>
           <t>ஒரு விவசாயியின் தோட்டத்தில் விளைந்திருந்த காய்களையும் கனிகளையும், கிழங்குகளையும் வயிறாரத் தின்று வாழ்ந்து  கொண்டிருந்தது ஒரு முயல்</t>
         </is>
       </c>
-      <c r="G288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -10195,12 +10195,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F289" t="inlineStr">
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr">
         <is>
           <t xml:space="preserve">வாழ் நாளெல்லாம் அந்தப் புலிக்குப் பயந்து கொண்டே இருக்க முடியாது. </t>
         </is>
       </c>
-      <c r="G289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -10228,12 +10228,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F290" t="inlineStr">
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="inlineStr">
         <is>
           <t xml:space="preserve">இவ்வளவு காலம் என்னைக்கண்டாலே ஓட்டம் எடுப்பாய். </t>
         </is>
       </c>
-      <c r="G290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -10261,12 +10261,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F291" t="inlineStr">
+      <c r="F291" t="inlineStr"/>
+      <c r="G291" t="inlineStr">
         <is>
           <t xml:space="preserve">கருத்த மண்சட்டியில் வெள்ளை வெளேரென வரகரிசிச்சோறு கொதித்துக் கொண்டிருந்தது. </t>
         </is>
       </c>
-      <c r="G291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -10294,12 +10294,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F292" t="inlineStr">
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr">
         <is>
           <t xml:space="preserve">பசுஞ்சாணம் மெழுகிய தரையில் மனைப்பலகையில் அமர்ந்து துளிரான தலைவாழை இலையை விரித்து நீர் தெளித்து, </t>
         </is>
       </c>
-      <c r="G292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -10327,12 +10327,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F293" t="inlineStr">
+      <c r="F293" t="inlineStr"/>
+      <c r="G293" t="inlineStr">
         <is>
           <t xml:space="preserve">மாமா:தஞ்சாவூர் மாவட்டத்தில் உள்ளது. திருச்சியிலிருந்து 20 கிமீ தொலைவில் உள்ளது. </t>
         </is>
       </c>
-      <c r="G293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -10360,12 +10360,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F294" t="inlineStr">
+      <c r="F294" t="inlineStr"/>
+      <c r="G294" t="inlineStr">
         <is>
           <t xml:space="preserve">அத்தை: எனக்குத் தெரியும் நான் கூறுகிறேன் கேளுங்கள். </t>
         </is>
       </c>
-      <c r="G294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -10393,12 +10393,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F295" t="inlineStr">
+      <c r="F295" t="inlineStr"/>
+      <c r="G295" t="inlineStr">
         <is>
           <t xml:space="preserve">என்னை வளர்ப்பவளே!  </t>
         </is>
       </c>
-      <c r="G295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -10426,12 +10426,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F296" t="inlineStr">
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="inlineStr">
         <is>
           <t xml:space="preserve">என் ஆவி கலந்தவளே!  </t>
         </is>
       </c>
-      <c r="G296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -10459,12 +10459,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F297" t="inlineStr">
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="inlineStr">
         <is>
           <t xml:space="preserve">என்னில் வளர்பவளே! </t>
         </is>
       </c>
-      <c r="G297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -10492,12 +10492,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F298" t="inlineStr">
+      <c r="F298" t="inlineStr"/>
+      <c r="G298" t="inlineStr">
         <is>
           <t xml:space="preserve">அன்னைத் தமிழே! </t>
         </is>
       </c>
-      <c r="G298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -10525,12 +10525,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F299" t="inlineStr">
+      <c r="F299" t="inlineStr"/>
+      <c r="G299" t="inlineStr">
         <is>
           <t xml:space="preserve">உலகில் பிறப்பெடுத்தேன்  </t>
         </is>
       </c>
-      <c r="G299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -10558,12 +10558,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F300" t="inlineStr">
+      <c r="F300" t="inlineStr"/>
+      <c r="G300" t="inlineStr">
         <is>
           <t xml:space="preserve">சொல்லில் விளையாடச் சொல்லித் தந்தவளே!  </t>
         </is>
       </c>
-      <c r="G300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -10591,12 +10591,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F301" t="inlineStr">
+      <c r="F301" t="inlineStr"/>
+      <c r="G301" t="inlineStr">
         <is>
           <t xml:space="preserve">பேசுதல் என்பது அடிப்படைத்திறன் எனில், பேச்சாற்றல் என்பது உயர்நிலைத் திறன். பேசுதலின் வளர்நிலையேபேச்சாற்றல். அத்தகைய பேச்சாற்றல்திறனைவளர்க்கும் பாடங்களுள் ஒன்று, இக்கவிதைப் பட்டிமன்றம். </t>
         </is>
       </c>
-      <c r="G301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -10624,12 +10624,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F302" t="inlineStr">
+      <c r="F302" t="inlineStr"/>
+      <c r="G302" t="inlineStr">
         <is>
           <t xml:space="preserve">ஆணிவேர் என்றே </t>
         </is>
       </c>
-      <c r="G302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -10657,12 +10657,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F303" t="inlineStr">
+      <c r="F303" t="inlineStr"/>
+      <c r="G303" t="inlineStr">
         <is>
           <t xml:space="preserve">அறிவின் துணை கொண்டே </t>
         </is>
       </c>
-      <c r="G303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -10690,12 +10690,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F304" t="inlineStr">
+      <c r="F304" t="inlineStr"/>
+      <c r="G304" t="inlineStr">
         <is>
           <t xml:space="preserve">ஆயிரம் கண்டுபிடிப்பால் தாமஸ் </t>
         </is>
       </c>
-      <c r="G304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -10723,12 +10723,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F305" t="inlineStr">
+      <c r="F305" t="inlineStr"/>
+      <c r="G305" t="inlineStr">
         <is>
           <t xml:space="preserve">அறிவுமிகு மனிதனாக </t>
         </is>
       </c>
-      <c r="G305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -10756,12 +10756,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F306" t="inlineStr">
+      <c r="F306" t="inlineStr"/>
+      <c r="G306" t="inlineStr">
         <is>
           <t xml:space="preserve">அத்தனையும் நம் கையில் </t>
         </is>
       </c>
-      <c r="G306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -10789,12 +10789,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F307" t="inlineStr">
+      <c r="F307" t="inlineStr"/>
+      <c r="G307" t="inlineStr">
         <is>
           <t xml:space="preserve">அகிலத்தில் உயர்ந்து நின்றால் </t>
         </is>
       </c>
-      <c r="G307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -10822,12 +10822,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F308" t="inlineStr">
+      <c r="F308" t="inlineStr"/>
+      <c r="G308" t="inlineStr">
         <is>
           <t xml:space="preserve">நடுவர் : இன்சுவையின் கவிதை </t>
         </is>
       </c>
-      <c r="G308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -10855,12 +10855,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F309" t="inlineStr">
+      <c r="F309" t="inlineStr"/>
+      <c r="G309" t="inlineStr">
         <is>
           <t xml:space="preserve">அடுத்து, ஒளிரும் கவிதையுடன் </t>
         </is>
       </c>
-      <c r="G309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -10888,12 +10888,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F310" t="inlineStr">
+      <c r="F310" t="inlineStr"/>
+      <c r="G310" t="inlineStr">
         <is>
           <t xml:space="preserve">மதியொளி : அகிலமெல்லாம் தமிழே மணக்கும்! </t>
         </is>
       </c>
-      <c r="G310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -10921,12 +10921,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F311" t="inlineStr">
+      <c r="F311" t="inlineStr"/>
+      <c r="G311" t="inlineStr">
         <is>
           <t xml:space="preserve">பண்புதான் வெற்றிப்படி என்றே </t>
         </is>
       </c>
-      <c r="G311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -10954,12 +10954,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F312" t="inlineStr">
+      <c r="F312" t="inlineStr"/>
+      <c r="G312" t="inlineStr">
         <is>
           <t xml:space="preserve">பறை சாற்ற வந்துள்ளேன். </t>
         </is>
       </c>
-      <c r="G312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -10987,12 +10987,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F313" t="inlineStr">
+      <c r="F313" t="inlineStr"/>
+      <c r="G313" t="inlineStr">
         <is>
           <t xml:space="preserve">நம்மை உயரத்திலே </t>
         </is>
       </c>
-      <c r="G313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -11020,12 +11020,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F314" t="inlineStr">
+      <c r="F314" t="inlineStr"/>
+      <c r="G314" t="inlineStr">
         <is>
           <t xml:space="preserve">நற்பண்பு புகுந்து விட்டால் </t>
         </is>
       </c>
-      <c r="G314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -11053,12 +11053,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F315" t="inlineStr">
+      <c r="F315" t="inlineStr"/>
+      <c r="G315" t="inlineStr">
         <is>
           <t xml:space="preserve">நற்பண்பு தூக்கிவிடும் </t>
         </is>
       </c>
-      <c r="G315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -11086,12 +11086,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F316" t="inlineStr">
+      <c r="F316" t="inlineStr"/>
+      <c r="G316" t="inlineStr">
         <is>
           <t xml:space="preserve">பண்பாலே சிறந்தவர் தாம் </t>
         </is>
       </c>
-      <c r="G316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -11119,12 +11119,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F317" t="inlineStr">
+      <c r="F317" t="inlineStr"/>
+      <c r="G317" t="inlineStr">
         <is>
           <t xml:space="preserve">நாவினிலே இனிமை வரும் </t>
         </is>
       </c>
-      <c r="G317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -11152,12 +11152,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F318" t="inlineStr">
+      <c r="F318" t="inlineStr"/>
+      <c r="G318" t="inlineStr">
         <is>
           <t xml:space="preserve">புத்தரோடு வள்ளுவரும் </t>
         </is>
       </c>
-      <c r="G318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -11185,12 +11185,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F319" t="inlineStr">
+      <c r="F319" t="inlineStr"/>
+      <c r="G319" t="inlineStr">
         <is>
           <t xml:space="preserve">போதித்ததும் நற்பண்பே..... </t>
         </is>
       </c>
-      <c r="G319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -11218,12 +11218,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F320" t="inlineStr">
+      <c r="F320" t="inlineStr"/>
+      <c r="G320" t="inlineStr">
         <is>
           <t xml:space="preserve">பலருண்டு நம்மிடையே </t>
         </is>
       </c>
-      <c r="G320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -11251,12 +11251,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F321" t="inlineStr">
+      <c r="F321" t="inlineStr"/>
+      <c r="G321" t="inlineStr">
         <is>
           <t xml:space="preserve">அருளப்பன் வருகின்றார் </t>
         </is>
       </c>
-      <c r="G321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -11284,12 +11284,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F322" t="inlineStr">
+      <c r="F322" t="inlineStr"/>
+      <c r="G322" t="inlineStr">
         <is>
           <t xml:space="preserve">நடுவர் : மிளிர்கின்ற தமிழ்க் கவிதை </t>
         </is>
       </c>
-      <c r="G322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -11317,12 +11317,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F323" t="inlineStr">
+      <c r="F323" t="inlineStr"/>
+      <c r="G323" t="inlineStr">
         <is>
           <t xml:space="preserve">மதியொளியின் அரும் கவிதை.... </t>
         </is>
       </c>
-      <c r="G323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -11350,12 +11350,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F324" t="inlineStr">
+      <c r="F324" t="inlineStr"/>
+      <c r="G324" t="inlineStr">
         <is>
           <t xml:space="preserve">செறிவாற்றல் கவிதையொன்றைச் </t>
         </is>
       </c>
-      <c r="G324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -11383,12 +11383,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F325" t="inlineStr">
+      <c r="F325" t="inlineStr"/>
+      <c r="G325" t="inlineStr">
         <is>
           <t xml:space="preserve">அறிவாற்றல் பயன் பேச </t>
         </is>
       </c>
-      <c r="G325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -11416,12 +11416,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F326" t="inlineStr">
+      <c r="F326" t="inlineStr"/>
+      <c r="G326" t="inlineStr">
         <is>
           <t xml:space="preserve">அருளப்பன் : அறிவாற்றல் உள்ளவன்தான் </t>
         </is>
       </c>
-      <c r="G326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -11449,12 +11449,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F327" t="inlineStr">
+      <c r="F327" t="inlineStr"/>
+      <c r="G327" t="inlineStr">
         <is>
           <t xml:space="preserve">ஆளுகின்றான் அண்டத்தை </t>
         </is>
       </c>
-      <c r="G327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -11482,12 +11482,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F328" t="inlineStr">
+      <c r="F328" t="inlineStr"/>
+      <c r="G328" t="inlineStr">
         <is>
           <t xml:space="preserve">வெறும் பண்பை வைத்துக்கொண்டு </t>
         </is>
       </c>
-      <c r="G328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -11515,12 +11515,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F329" t="inlineStr">
+      <c r="F329" t="inlineStr"/>
+      <c r="G329" t="inlineStr">
         <is>
           <t xml:space="preserve">பெரும் பந்தல் போடலாமோ? </t>
         </is>
       </c>
-      <c r="G329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -11548,12 +11548,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F330" t="inlineStr">
+      <c r="F330" t="inlineStr"/>
+      <c r="G330" t="inlineStr">
         <is>
           <t xml:space="preserve">கூறும் பண்பில் நம் </t>
         </is>
       </c>
-      <c r="G330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -11581,12 +11581,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F331" t="inlineStr">
+      <c r="F331" t="inlineStr"/>
+      <c r="G331" t="inlineStr">
         <is>
           <t xml:space="preserve">﻿நல்லவன் இருந்தால் </t>
         </is>
       </c>
-      <c r="G331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -11614,12 +11614,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F332" t="inlineStr">
+      <c r="F332" t="inlineStr"/>
+      <c r="G332" t="inlineStr">
         <is>
           <t xml:space="preserve">நாடென்ன முன்னேறுமோ? </t>
         </is>
       </c>
-      <c r="G332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -11647,12 +11647,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F333" t="inlineStr">
+      <c r="F333" t="inlineStr"/>
+      <c r="G333" t="inlineStr">
         <is>
           <t xml:space="preserve">வல்லவன் வகுத்ததன்றோ </t>
         </is>
       </c>
-      <c r="G333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -11680,12 +11680,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F334" t="inlineStr">
+      <c r="F334" t="inlineStr"/>
+      <c r="G334" t="inlineStr">
         <is>
           <t xml:space="preserve">வளமான இவ்வுலகு..... </t>
         </is>
       </c>
-      <c r="G334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -11713,12 +11713,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F335" t="inlineStr">
+      <c r="F335" t="inlineStr"/>
+      <c r="G335" t="inlineStr">
         <is>
           <t xml:space="preserve">தூண் போன்ற அறிவேதான் </t>
         </is>
       </c>
-      <c r="G335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -11746,12 +11746,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F336" t="inlineStr">
+      <c r="F336" t="inlineStr"/>
+      <c r="G336" t="inlineStr">
         <is>
           <t xml:space="preserve">நடுவர் : பண்பின் பெருஞ்சிறப்பைப் </t>
         </is>
       </c>
-      <c r="G336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -11779,12 +11779,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F337" t="inlineStr">
+      <c r="F337" t="inlineStr"/>
+      <c r="G337" t="inlineStr">
         <is>
           <t xml:space="preserve">﻿சலீமா : பண்பிலான் பெற்ற செல்வம் </t>
         </is>
       </c>
-      <c r="G337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -11812,12 +11812,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F338" t="inlineStr">
+      <c r="F338" t="inlineStr"/>
+      <c r="G338" t="inlineStr">
         <is>
           <t xml:space="preserve">பயனில்லை உலகோர்க்கே </t>
         </is>
       </c>
-      <c r="G338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -11845,12 +11845,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F339" t="inlineStr">
+      <c r="F339" t="inlineStr"/>
+      <c r="G339" t="inlineStr">
         <is>
           <t xml:space="preserve">பொழிந்திடவே வருகின்றார் </t>
         </is>
       </c>
-      <c r="G339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -11878,12 +11878,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F340" t="inlineStr">
+      <c r="F340" t="inlineStr"/>
+      <c r="G340" t="inlineStr">
         <is>
           <t xml:space="preserve">பண்பேதான் அன்பை நல்கும் </t>
         </is>
       </c>
-      <c r="G340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -11911,12 +11911,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F341" t="inlineStr">
+      <c r="F341" t="inlineStr"/>
+      <c r="G341" t="inlineStr">
         <is>
           <t xml:space="preserve">பன்மடங்கு உயர்வைத் தரும் </t>
         </is>
       </c>
-      <c r="G341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -11944,12 +11944,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F342" t="inlineStr">
+      <c r="F342" t="inlineStr"/>
+      <c r="G342" t="inlineStr">
         <is>
           <t xml:space="preserve">உண்மை சொன்னேன் யாவர்க்கும் </t>
         </is>
       </c>
-      <c r="G342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -11977,12 +11977,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F343" t="inlineStr">
+      <c r="F343" t="inlineStr"/>
+      <c r="G343" t="inlineStr">
         <is>
           <t xml:space="preserve">அன்பின் மிகுதியால் அதியமான் </t>
         </is>
       </c>
-      <c r="G343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -12010,12 +12010,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F344" t="inlineStr">
+      <c r="F344" t="inlineStr"/>
+      <c r="G344" t="inlineStr">
         <is>
           <t xml:space="preserve">உவந்தளித்தான் ஔவைக்கு </t>
         </is>
       </c>
-      <c r="G344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -12043,12 +12043,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F345" t="inlineStr">
+      <c r="F345" t="inlineStr"/>
+      <c r="G345" t="inlineStr">
         <is>
           <t xml:space="preserve">அத்தனையும் எளியோர்க்கு </t>
         </is>
       </c>
-      <c r="G345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -12076,12 +12076,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F346" t="inlineStr">
+      <c r="F346" t="inlineStr"/>
+      <c r="G346" t="inlineStr">
         <is>
           <t xml:space="preserve">உயிர் காக்கும் நெல்லிக்கனியை </t>
         </is>
       </c>
-      <c r="G346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -12109,12 +12109,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F347" t="inlineStr">
+      <c r="F347" t="inlineStr"/>
+      <c r="G347" t="inlineStr">
         <is>
           <t xml:space="preserve">குணமென்னும் நற்பண்பே </t>
         </is>
       </c>
-      <c r="G347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -12142,12 +12142,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F348" t="inlineStr">
+      <c r="F348" t="inlineStr"/>
+      <c r="G348" t="inlineStr">
         <is>
           <t xml:space="preserve">அன்னை தெரசா பெற்றுத் தந்தார் </t>
         </is>
       </c>
-      <c r="G348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -12175,12 +12175,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F349" t="inlineStr">
+      <c r="F349" t="inlineStr"/>
+      <c r="G349" t="inlineStr">
         <is>
           <t xml:space="preserve">நடுவர் : எல்லோரும் சிறப்பாக </t>
         </is>
       </c>
-      <c r="G349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -12208,12 +12208,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F350" t="inlineStr">
+      <c r="F350" t="inlineStr"/>
+      <c r="G350" t="inlineStr">
         <is>
           <t xml:space="preserve">நல்லோரே போற்றும் வண்ணம் </t>
         </is>
       </c>
-      <c r="G350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -12241,12 +12241,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F351" t="inlineStr">
+      <c r="F351" t="inlineStr"/>
+      <c r="G351" t="inlineStr">
         <is>
           <t xml:space="preserve">என்னுடைய தீர்ப்பிற்கு </t>
         </is>
       </c>
-      <c r="G351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -12274,12 +12274,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F352" t="inlineStr">
+      <c r="F352" t="inlineStr"/>
+      <c r="G352" t="inlineStr">
         <is>
           <t xml:space="preserve">நற்கவிதை வாசித்தார்கள்..... </t>
         </is>
       </c>
-      <c r="G352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -12307,12 +12307,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F353" t="inlineStr">
+      <c r="F353" t="inlineStr"/>
+      <c r="G353" t="inlineStr">
         <is>
           <t xml:space="preserve">கண்ணுக்கு இருவிழி </t>
         </is>
       </c>
-      <c r="G353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -12340,12 +12340,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F354" t="inlineStr">
+      <c r="F354" t="inlineStr"/>
+      <c r="G354" t="inlineStr">
         <is>
           <t xml:space="preserve">கல்வியின் நேர்விழி </t>
         </is>
       </c>
-      <c r="G354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -12373,12 +12373,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F355" t="inlineStr">
+      <c r="F355" t="inlineStr"/>
+      <c r="G355" t="inlineStr">
         <is>
           <t xml:space="preserve">இசைந்தே தான் வருகின்றேன்... </t>
         </is>
       </c>
-      <c r="G355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -12406,12 +12406,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F356" t="inlineStr">
+      <c r="F356" t="inlineStr"/>
+      <c r="G356" t="inlineStr">
         <is>
           <t xml:space="preserve">அறிவும் பண்பும் </t>
         </is>
       </c>
-      <c r="G356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -12439,12 +12439,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F357" t="inlineStr">
+      <c r="F357" t="inlineStr"/>
+      <c r="G357" t="inlineStr">
         <is>
           <t xml:space="preserve">சமமாக வைத்தேதான் </t>
         </is>
       </c>
-      <c r="G357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -12472,12 +12472,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F358" t="inlineStr">
+      <c r="F358" t="inlineStr"/>
+      <c r="G358" t="inlineStr">
         <is>
           <t xml:space="preserve">பொறி ஐந்தும் பண்பாகப் </t>
         </is>
       </c>
-      <c r="G358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -12505,12 +12505,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F359" t="inlineStr">
+      <c r="F359" t="inlineStr"/>
+      <c r="G359" t="inlineStr">
         <is>
           <t xml:space="preserve">பார் முழுவதும் அறிவாக </t>
         </is>
       </c>
-      <c r="G359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -12538,12 +12538,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F360" t="inlineStr">
+      <c r="F360" t="inlineStr"/>
+      <c r="G360" t="inlineStr">
         <is>
           <t xml:space="preserve">வலம் வருவோம் நாமே </t>
         </is>
       </c>
-      <c r="G360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -12571,12 +12571,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F361" t="inlineStr">
+      <c r="F361" t="inlineStr"/>
+      <c r="G361" t="inlineStr">
         <is>
           <t xml:space="preserve">நல்ல தீர்ப்பு கூறி </t>
         </is>
       </c>
-      <c r="G361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -12604,12 +12604,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F362" t="inlineStr">
+      <c r="F362" t="inlineStr"/>
+      <c r="G362" t="inlineStr">
         <is>
           <t xml:space="preserve">உளம் நிறை வாழ்த்தோடு </t>
         </is>
       </c>
-      <c r="G362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -12637,12 +12637,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F363" t="inlineStr">
+      <c r="F363" t="inlineStr"/>
+      <c r="G363" t="inlineStr">
         <is>
           <t xml:space="preserve">நலம் இரண்டும் தானென்று </t>
         </is>
       </c>
-      <c r="G363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -12670,12 +12670,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F364" t="inlineStr">
+      <c r="F364" t="inlineStr"/>
+      <c r="G364" t="inlineStr">
         <is>
           <t xml:space="preserve">நானும் விடைபெறுகின்றேன்..... </t>
         </is>
       </c>
-      <c r="G364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -12703,12 +12703,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F365" t="inlineStr">
+      <c r="F365" t="inlineStr"/>
+      <c r="G365" t="inlineStr">
         <is>
           <t xml:space="preserve">என்ன சத்தம்...  </t>
         </is>
       </c>
-      <c r="G365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -12736,12 +12736,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F366" t="inlineStr">
+      <c r="F366" t="inlineStr"/>
+      <c r="G366" t="inlineStr">
         <is>
           <t xml:space="preserve">செழியன் ஆடுகளை ஓட்டிக்கொண்டு பாட்டியுடன் வீட்டிற்குக் கிளம்பினான். தூரத்தில் எங்கோ சிங்கம் முழங்கும் சத்தம் கேட்டது. அந்தச் சத்தத்தைக் கேட்டவுடன் காடே பரபரப்பாகி விட்டது. பறவைகள் இறக்கைகளைப் படபடவென அடித்துக் கொண்டு இங்குமங்கும் பறந்தன. யானை பிளிறியது; ஆந்தை அலறியது; கீரிப்பிள்ளையும் செடிகளின் மறைவிலிருந்து ஓடியது மயில் அகவியது; பாம்பும் தன் புற்றிலிருந்து வெளியே வந்து சீறியது; குதிரை கனைத்தது. இவற்றை எல்லாம் கேட்ட செழியனுக்குப் பயத்தால் நாக்கு வறண்டது. தான் வைத்திருந்த தண்ணீரைக் குடித்தான். </t>
         </is>
       </c>
-      <c r="G366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -12769,12 +12769,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F367" t="inlineStr">
+      <c r="F367" t="inlineStr"/>
+      <c r="G367" t="inlineStr">
         <is>
           <t xml:space="preserve">சிறிது நேரத்திற்குப் பிறகு, செழியனையையும் , பூவிழியையும், பாட்டியையும் சாப்பிட வாருங்கள் என்று அம்மா அழைத்தார். அம்மாவின் குரலைக் கேட்டதும் இருவரும் சென்று கொடுத்த உணவை உண்டனர். </t>
         </is>
       </c>
-      <c r="G367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -12802,12 +12802,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F368" t="inlineStr">
+      <c r="F368" t="inlineStr"/>
+      <c r="G368" t="inlineStr">
         <is>
           <t xml:space="preserve">வாழைத் தோட்டத்திலிருந்த தண்ணீர்த் தொட்டியில் செழியன் குளித்துவிட்டு வந்தான். அம்மா கொடுத்த முறுக்கைத் தின்றான். அப்போது தங்கை பூவிழி பால் பருகிக் கொண்டிருந்தாள். </t>
         </is>
       </c>
-      <c r="G368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -12835,12 +12835,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F369" t="inlineStr">
+      <c r="F369" t="inlineStr"/>
+      <c r="G369" t="inlineStr">
         <is>
           <t xml:space="preserve">மரபுச் சொற்கள் </t>
         </is>
       </c>
-      <c r="G369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -12868,12 +12868,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F370" t="inlineStr">
+      <c r="F370" t="inlineStr"/>
+      <c r="G370" t="inlineStr">
         <is>
           <t xml:space="preserve">எலியின் இந்த சத்தம், பாட்டியின் கதைக்குப் பின்னணி சேர்ப்பதுபோல் இருந்தது.நாய் குரைக்கும் சத்தத்தைக் கேட்டு வெளியே வந்து பார்த்தான். அங்கே பூனை ஒன்று சீறுவதைக் கண்டு நாய் குரைத்த காரணம் அறிந்தான். இரண்டையும் அருகிலிருந்த தென்னந் தோப்பின் பக்கம் விரட்டிவிட்டு வீட்டிற்கு வந்து படுத்துக் கொண்டான். பாட்டியும், தங்கையும் முன்பே தூங்கிவிட்டனர். </t>
         </is>
       </c>
-      <c r="G370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -12901,12 +12901,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F371" t="inlineStr">
+      <c r="F371" t="inlineStr"/>
+      <c r="G371" t="inlineStr">
         <is>
           <t xml:space="preserve">புலி உறுமும் </t>
         </is>
       </c>
-      <c r="G371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -12934,12 +12934,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F372" t="inlineStr">
+      <c r="F372" t="inlineStr"/>
+      <c r="G372" t="inlineStr">
         <is>
           <t xml:space="preserve">குரங்கு அலப்பும் </t>
         </is>
       </c>
-      <c r="G372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -12967,12 +12967,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F373" t="inlineStr">
+      <c r="F373" t="inlineStr"/>
+      <c r="G373" t="inlineStr">
         <is>
           <t xml:space="preserve">யானை பிளிறும் </t>
         </is>
       </c>
-      <c r="G373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -13000,12 +13000,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F374" t="inlineStr">
+      <c r="F374" t="inlineStr"/>
+      <c r="G374" t="inlineStr">
         <is>
           <t xml:space="preserve">ஒலி மரபுச் சொற்கள் </t>
         </is>
       </c>
-      <c r="G374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -13033,12 +13033,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F375" t="inlineStr">
+      <c r="F375" t="inlineStr"/>
+      <c r="G375" t="inlineStr">
         <is>
           <t xml:space="preserve">ஆந்தை அலறும் </t>
         </is>
       </c>
-      <c r="G375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -13066,12 +13066,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F376" t="inlineStr">
+      <c r="F376" t="inlineStr"/>
+      <c r="G376" t="inlineStr">
         <is>
           <t xml:space="preserve">சிங்கம் கர்ச்சிக்கும், முழங்கும் </t>
         </is>
       </c>
-      <c r="G376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -13099,12 +13099,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F377" t="inlineStr">
+      <c r="F377" t="inlineStr"/>
+      <c r="G377" t="inlineStr">
         <is>
           <t xml:space="preserve">நாய் குரைக்கும் </t>
         </is>
       </c>
-      <c r="G377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -13132,12 +13132,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F378" t="inlineStr">
+      <c r="F378" t="inlineStr"/>
+      <c r="G378" t="inlineStr">
         <is>
           <t xml:space="preserve">மயில் அகவும் </t>
         </is>
       </c>
-      <c r="G378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -13165,12 +13165,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F379" t="inlineStr">
+      <c r="F379" t="inlineStr"/>
+      <c r="G379" t="inlineStr">
         <is>
           <t xml:space="preserve">ஆடு கத்தும் </t>
         </is>
       </c>
-      <c r="G379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -13198,12 +13198,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F380" t="inlineStr">
+      <c r="F380" t="inlineStr"/>
+      <c r="G380" t="inlineStr">
         <is>
           <t xml:space="preserve">விலங்குகளின் இளமைப்பெயர் மரபுச் சொற்கள் </t>
         </is>
       </c>
-      <c r="G380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -13231,12 +13231,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F381" t="inlineStr">
+      <c r="F381" t="inlineStr"/>
+      <c r="G381" t="inlineStr">
         <is>
           <t xml:space="preserve">ஆட்டுக் குட்டி </t>
         </is>
       </c>
-      <c r="G381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -13264,12 +13264,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F382" t="inlineStr">
+      <c r="F382" t="inlineStr"/>
+      <c r="G382" t="inlineStr">
         <is>
           <t xml:space="preserve">கோழிக் குஞ்சு </t>
         </is>
       </c>
-      <c r="G382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -13297,12 +13297,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F383" t="inlineStr">
+      <c r="F383" t="inlineStr"/>
+      <c r="G383" t="inlineStr">
         <is>
           <t xml:space="preserve">யானைக் கன்று </t>
         </is>
       </c>
-      <c r="G383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -13330,12 +13330,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F384" t="inlineStr">
+      <c r="F384" t="inlineStr"/>
+      <c r="G384" t="inlineStr">
         <is>
           <t xml:space="preserve">குதிரைக் குட்டி </t>
         </is>
       </c>
-      <c r="G384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -13363,12 +13363,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F385" t="inlineStr">
+      <c r="F385" t="inlineStr"/>
+      <c r="G385" t="inlineStr">
         <is>
           <t xml:space="preserve">சிங்கக் குருளை </t>
         </is>
       </c>
-      <c r="G385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -13396,12 +13396,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F386" t="inlineStr">
+      <c r="F386" t="inlineStr"/>
+      <c r="G386" t="inlineStr">
         <is>
           <t xml:space="preserve">குரங்குக் குட்டி </t>
         </is>
       </c>
-      <c r="G386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -13429,12 +13429,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F387" t="inlineStr">
+      <c r="F387" t="inlineStr"/>
+      <c r="G387" t="inlineStr">
         <is>
           <t xml:space="preserve">கீரிப் பிள்ளை </t>
         </is>
       </c>
-      <c r="G387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -13462,12 +13462,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F388" t="inlineStr">
+      <c r="F388" t="inlineStr"/>
+      <c r="G388" t="inlineStr">
         <is>
           <t xml:space="preserve">மான் கன்று </t>
         </is>
       </c>
-      <c r="G388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -13495,12 +13495,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F389" t="inlineStr">
+      <c r="F389" t="inlineStr"/>
+      <c r="G389" t="inlineStr">
         <is>
           <t xml:space="preserve">﻿வினைமரபுச் சொற்கள் </t>
         </is>
       </c>
-      <c r="G389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -13528,12 +13528,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F390" t="inlineStr">
+      <c r="F390" t="inlineStr"/>
+      <c r="G390" t="inlineStr">
         <is>
           <t xml:space="preserve">சோறு உண்டான் </t>
         </is>
       </c>
-      <c r="G390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -13561,12 +13561,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F391" t="inlineStr">
+      <c r="F391" t="inlineStr"/>
+      <c r="G391" t="inlineStr">
         <is>
           <t xml:space="preserve">அம்பு எய்தார் </t>
         </is>
       </c>
-      <c r="G391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -13594,12 +13594,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F392" t="inlineStr">
+      <c r="F392" t="inlineStr"/>
+      <c r="G392" t="inlineStr">
         <is>
           <t xml:space="preserve">ஆடை நெய்தார் </t>
         </is>
       </c>
-      <c r="G392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -13627,12 +13627,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F393" t="inlineStr">
+      <c r="F393" t="inlineStr"/>
+      <c r="G393" t="inlineStr">
         <is>
           <t xml:space="preserve">பூ பறித்தாள் </t>
         </is>
       </c>
-      <c r="G393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -13660,12 +13660,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F394" t="inlineStr">
+      <c r="F394" t="inlineStr"/>
+      <c r="G394" t="inlineStr">
         <is>
           <t xml:space="preserve">கூடை முடைந்தார் </t>
         </is>
       </c>
-      <c r="G394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -13693,12 +13693,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F395" t="inlineStr">
+      <c r="F395" t="inlineStr"/>
+      <c r="G395" t="inlineStr">
         <is>
           <t xml:space="preserve">மாத்திரை விழுங்கினான் </t>
         </is>
       </c>
-      <c r="G395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -13726,12 +13726,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F396" t="inlineStr">
+      <c r="F396" t="inlineStr"/>
+      <c r="G396" t="inlineStr">
         <is>
           <t xml:space="preserve">சுவர் எழுப்பினார் </t>
         </is>
       </c>
-      <c r="G396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -13759,12 +13759,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F397" t="inlineStr">
+      <c r="F397" t="inlineStr"/>
+      <c r="G397" t="inlineStr">
         <is>
           <t xml:space="preserve">நீர் குடித்தான் </t>
         </is>
       </c>
-      <c r="G397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -13792,12 +13792,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F398" t="inlineStr">
+      <c r="F398" t="inlineStr"/>
+      <c r="G398" t="inlineStr">
         <is>
           <t xml:space="preserve">முறுக்கு தின்றாள் </t>
         </is>
       </c>
-      <c r="G398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -13825,12 +13825,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F399" t="inlineStr">
+      <c r="F399" t="inlineStr"/>
+      <c r="G399" t="inlineStr">
         <is>
           <t xml:space="preserve">மா, பலா, வாழை இலை </t>
         </is>
       </c>
-      <c r="G399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -13858,12 +13858,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F400" t="inlineStr">
+      <c r="F400" t="inlineStr"/>
+      <c r="G400" t="inlineStr">
         <is>
           <t xml:space="preserve">தாவரங்களின் உறுப்புப்பெயர் மரபுச் சொற்கள் </t>
         </is>
       </c>
-      <c r="G400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -13891,12 +13891,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F401" t="inlineStr">
+      <c r="F401" t="inlineStr"/>
+      <c r="G401" t="inlineStr">
         <is>
           <t xml:space="preserve">கம்பு, கேழ்வரகு, சோளம் தட்டை </t>
         </is>
       </c>
-      <c r="G401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -13924,12 +13924,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F402" t="inlineStr">
+      <c r="F402" t="inlineStr"/>
+      <c r="G402" t="inlineStr">
         <is>
           <t xml:space="preserve">நெல், புல், தினை தாள் </t>
         </is>
       </c>
-      <c r="G402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -13957,12 +13957,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F403" t="inlineStr">
+      <c r="F403" t="inlineStr"/>
+      <c r="G403" t="inlineStr">
         <is>
           <t xml:space="preserve">பூச்சிகள், பறவைகள், விலங்குகள் – இருப்பிட மரபுச் சொற்கள் </t>
         </is>
       </c>
-      <c r="G403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -13990,12 +13990,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F404" t="inlineStr">
+      <c r="F404" t="inlineStr"/>
+      <c r="G404" t="inlineStr">
         <is>
           <t xml:space="preserve">கரையான் புற்று </t>
         </is>
       </c>
-      <c r="G404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -14023,12 +14023,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F405" t="inlineStr">
+      <c r="F405" t="inlineStr"/>
+      <c r="G405" t="inlineStr">
         <is>
           <t xml:space="preserve">மாட்டுத் தொழுவம் </t>
         </is>
       </c>
-      <c r="G405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -14056,12 +14056,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F406" t="inlineStr">
+      <c r="F406" t="inlineStr"/>
+      <c r="G406" t="inlineStr">
         <is>
           <t xml:space="preserve">ஆட்டுப் பட்டி </t>
         </is>
       </c>
-      <c r="G406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -14089,12 +14089,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F407" t="inlineStr">
+      <c r="F407" t="inlineStr"/>
+      <c r="G407" t="inlineStr">
         <is>
           <t xml:space="preserve">கோழிப் பண்ணை </t>
         </is>
       </c>
-      <c r="G407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -14122,12 +14122,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F408" t="inlineStr">
+      <c r="F408" t="inlineStr"/>
+      <c r="G408" t="inlineStr">
         <is>
           <t xml:space="preserve">குதிரைக் கொட்டில் </t>
         </is>
       </c>
-      <c r="G408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -14155,12 +14155,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F409" t="inlineStr">
+      <c r="F409" t="inlineStr"/>
+      <c r="G409" t="inlineStr">
         <is>
           <t xml:space="preserve">சிலந்தி வலை </t>
         </is>
       </c>
-      <c r="G409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -14188,12 +14188,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F410" t="inlineStr">
+      <c r="F410" t="inlineStr"/>
+      <c r="G410" t="inlineStr">
         <is>
           <t xml:space="preserve">எலி வளை </t>
         </is>
       </c>
-      <c r="G410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -14221,12 +14221,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F411" t="inlineStr">
+      <c r="F411" t="inlineStr"/>
+      <c r="G411" t="inlineStr">
         <is>
           <t xml:space="preserve">நண்டு வளை </t>
         </is>
       </c>
-      <c r="G411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -14254,12 +14254,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F412" t="inlineStr">
+      <c r="F412" t="inlineStr"/>
+      <c r="G412" t="inlineStr">
         <is>
           <t xml:space="preserve">குருவிக் கூடு </t>
         </is>
       </c>
-      <c r="G412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -14287,12 +14287,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F413" t="inlineStr">
+      <c r="F413" t="inlineStr"/>
+      <c r="G413" t="inlineStr">
         <is>
           <t xml:space="preserve">அடக்கம் உடையார் அறிவிலர் என்றெண்ணிக் </t>
         </is>
       </c>
-      <c r="G413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -14320,12 +14320,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F414" t="inlineStr">
+      <c r="F414" t="inlineStr"/>
+      <c r="G414" t="inlineStr">
         <is>
           <t xml:space="preserve">கடக்கக் கருதவும் வேண்டா – மடைத்தலையில் </t>
         </is>
       </c>
-      <c r="G414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -14353,12 +14353,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F415" t="inlineStr">
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="inlineStr">
         <is>
           <t xml:space="preserve">ஓடுமீன் ஓட உறுமீன் வருமளவும் </t>
         </is>
       </c>
-      <c r="G415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -14386,12 +14386,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F416" t="inlineStr">
+      <c r="F416" t="inlineStr"/>
+      <c r="G416" t="inlineStr">
         <is>
           <t xml:space="preserve">அதுபோலவே வேலைக்காரர்கள் செய்தனர். அங்கே காத்திருந்த சிறுவர் சிறுமியர் அவர்களைச் சூழ்ந்து கொண்டனர். வேலைக்காரர்கள் கூடையினை அவர்கள் முன் வைத்தனர் </t>
         </is>
       </c>
-      <c r="G416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -14419,12 +14419,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F417" t="inlineStr">
+      <c r="F417" t="inlineStr"/>
+      <c r="G417" t="inlineStr">
         <is>
           <t xml:space="preserve">மாளிகைக்குத் திரும்பிய அவர், தம் வேலைக்காரர்களை அழைத்தார். இந்த ஊரில் உள்ள குழந்தைகளின் எண்ணிக்கையைக் கணக்கெடுத்துக்கொள். ஆளுக்கொரு கொழுக்கட்டை கிடைக்க வேண்டும். நாளையிலிருந்து கொழுக்கட்டைகளைக் கூடையில் சரியான எண்ணிக்கையில் வைத்துக்கொண்டு வீட்டிற்கு வெளியே இருக்க வேண்டும் என்றார். </t>
         </is>
       </c>
-      <c r="G417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -14452,12 +14452,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F418" t="inlineStr">
+      <c r="F418" t="inlineStr"/>
+      <c r="G418" t="inlineStr">
         <is>
           <t xml:space="preserve">எல்லாரும் எடுத்துச் சென்றது போக மீதி இருந்த சிறிய கொழுக்கட்டையை எடுத்துக் கொண்டு அங்கிருந்து மகிழ்ச்சியுடன் சென்றாள் அவள். எல்லாவற்றையும் கவனித்துக் கொண்டிருந்தார் பணக்காரர். </t>
         </is>
       </c>
-      <c r="G418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -14485,12 +14485,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F419" t="inlineStr">
+      <c r="F419" t="inlineStr"/>
+      <c r="G419" t="inlineStr">
         <is>
           <t xml:space="preserve">அதற்கு அவர், இது தங்கக் காசு என்று இளவேனிலிடம் கூறிவிட்டு, இது எப்படி கொழுக்கட்டைக்குள் வந்திருக்கும் என்று யோசித்தவாறே, இந்தக் கொழுக்கட்டையை யார் கொடுத்தார்களோ அவர்களிடமே சென்று கொடுத்துவிடு என்றார். </t>
         </is>
       </c>
-      <c r="G419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -14518,12 +14518,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F420" t="inlineStr">
+      <c r="F420" t="inlineStr"/>
+      <c r="G420" t="inlineStr">
         <is>
           <t xml:space="preserve">அந்தத் தங்கக்காசை எடுத்துக் கொண்டு பணக்காரரின் வீட்டிற்கு வந்தாள் சிறுமி. ஐயா! நான் எடுத்துச் சென்ற கொழுக்கட்டைக்குள் இந்தத் தங்கக் காசு இருந்தது, பெற்றுக் கொள்ளுங்கள் என்றாள். </t>
         </is>
       </c>
-      <c r="G420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -14551,12 +14551,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F421" t="inlineStr">
+      <c r="F421" t="inlineStr"/>
+      <c r="G421" t="inlineStr">
         <is>
           <t xml:space="preserve">இத்தொடரில் , </t>
         </is>
       </c>
-      <c r="G421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -14584,12 +14584,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F422" t="inlineStr">
+      <c r="F422" t="inlineStr"/>
+      <c r="G422" t="inlineStr">
         <is>
           <t xml:space="preserve">2. மாடு புல் மேய்ந்தது. </t>
         </is>
       </c>
-      <c r="G422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -14617,12 +14617,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F423" t="inlineStr">
+      <c r="F423" t="inlineStr"/>
+      <c r="G423" t="inlineStr">
         <is>
           <t xml:space="preserve">ஒன்றன் பெயரைக் குறிப்பது பெயர்ச்சொல் </t>
         </is>
       </c>
-      <c r="G423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -14650,12 +14650,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F424" t="inlineStr">
+      <c r="F424" t="inlineStr"/>
+      <c r="G424" t="inlineStr">
         <is>
           <t xml:space="preserve">மாடு, புல் – பெயர்ச்சொற்கள் </t>
         </is>
       </c>
-      <c r="G424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -14683,12 +14683,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F425" t="inlineStr">
+      <c r="F425" t="inlineStr"/>
+      <c r="G425" t="inlineStr">
         <is>
           <t xml:space="preserve">அல்லும் பகலும் அலைகடலே – உனக்கு </t>
         </is>
       </c>
-      <c r="G425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -14716,12 +14716,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F426" t="inlineStr">
+      <c r="F426" t="inlineStr"/>
+      <c r="G426" t="inlineStr">
         <is>
           <t xml:space="preserve">எல்லை அறியாய் பெருங்கடலே – நீதான் </t>
         </is>
       </c>
-      <c r="G426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -14749,12 +14749,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F427" t="inlineStr">
+      <c r="F427" t="inlineStr"/>
+      <c r="G427" t="inlineStr">
         <is>
           <t xml:space="preserve">இரவும் உறங்காயோ? கடலே </t>
         </is>
       </c>
-      <c r="G427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -14782,12 +14782,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F428" t="inlineStr">
+      <c r="F428" t="inlineStr"/>
+      <c r="G428" t="inlineStr">
         <is>
           <t xml:space="preserve">அலுப்பும் இலையோ கருங்கடலே </t>
         </is>
       </c>
-      <c r="G428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -14815,12 +14815,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F429" t="inlineStr">
+      <c r="F429" t="inlineStr"/>
+      <c r="G429" t="inlineStr">
         <is>
           <t xml:space="preserve">புரவி நிரைதாமோ? கடலே </t>
         </is>
       </c>
-      <c r="G429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -14848,12 +14848,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F430" t="inlineStr">
+      <c r="F430" t="inlineStr"/>
+      <c r="G430" t="inlineStr">
         <is>
           <t xml:space="preserve">பொங்கு திரைகளோ? கடலே – அவை </t>
         </is>
       </c>
-      <c r="G430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -14881,12 +14881,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F431" t="inlineStr">
+      <c r="F431" t="inlineStr"/>
+      <c r="G431" t="inlineStr">
         <is>
           <t xml:space="preserve">எங்கும் உனதொலியோ? கடலே! – அன்றி </t>
         </is>
       </c>
-      <c r="G431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -14914,12 +14914,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F432" t="inlineStr">
+      <c r="F432" t="inlineStr"/>
+      <c r="G432" t="inlineStr">
         <is>
           <t xml:space="preserve">மகர மீனுலவும் கடலே! </t>
         </is>
       </c>
-      <c r="G432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -14947,12 +14947,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F433" t="inlineStr">
+      <c r="F433" t="inlineStr"/>
+      <c r="G433" t="inlineStr">
         <is>
           <t xml:space="preserve">விளையாடற் குதவும் கடலே! </t>
         </is>
       </c>
-      <c r="G433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -14980,12 +14980,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F434" t="inlineStr">
+      <c r="F434" t="inlineStr"/>
+      <c r="G434" t="inlineStr">
         <is>
           <t xml:space="preserve">விலைகொள் முத்தளிக்கும் கடலே! – சிப்பி </t>
         </is>
       </c>
-      <c r="G434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -15013,12 +15013,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F435" t="inlineStr">
+      <c r="F435" t="inlineStr"/>
+      <c r="G435" t="inlineStr">
         <is>
           <t xml:space="preserve">வாங்கி வைப்பதும் நீ, கடலே! </t>
         </is>
       </c>
-      <c r="G435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -15046,12 +15046,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F436" t="inlineStr">
+      <c r="F436" t="inlineStr"/>
+      <c r="G436" t="inlineStr">
         <is>
           <t xml:space="preserve">வழுத்து மகிமையெலாம் கடலே! – எவர் </t>
         </is>
       </c>
-      <c r="G436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -15079,12 +15079,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F437" t="inlineStr">
+      <c r="F437" t="inlineStr"/>
+      <c r="G437" t="inlineStr">
         <is>
           <t xml:space="preserve">மழைக்கு மூலமும் நீ கடலே! – அதை </t>
         </is>
       </c>
-      <c r="G437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -15112,12 +15112,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F438" t="inlineStr">
+      <c r="F438" t="inlineStr"/>
+      <c r="G438" t="inlineStr">
         <is>
           <t xml:space="preserve">மதித்து முடிக்கவலார் கடலே! </t>
         </is>
       </c>
-      <c r="G438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -15145,12 +15145,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F439" t="inlineStr">
+      <c r="F439" t="inlineStr"/>
+      <c r="G439" t="inlineStr">
         <is>
           <t xml:space="preserve">சரியாகக் கூறினாய். இதோ உனக்கு மாங்காய் பறித்துத் தருகிறேன். </t>
         </is>
       </c>
-      <c r="G439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -15178,12 +15178,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F440" t="inlineStr">
+      <c r="F440" t="inlineStr"/>
+      <c r="G440" t="inlineStr">
         <is>
           <t xml:space="preserve">யானை வரும் பின்னே மணியோசை வரும் முன்னே! </t>
         </is>
       </c>
-      <c r="G440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -15211,12 +15211,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F441" t="inlineStr">
+      <c r="F441" t="inlineStr"/>
+      <c r="G441" t="inlineStr">
         <is>
           <t xml:space="preserve">ஐ.......! ரொம்ப நன்றி செல்லம்மா </t>
         </is>
       </c>
-      <c r="G441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -15244,12 +15244,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F442" t="inlineStr">
+      <c r="F442" t="inlineStr"/>
+      <c r="G442" t="inlineStr">
         <is>
           <t xml:space="preserve">யார் வந்திருப்பது? </t>
         </is>
       </c>
-      <c r="G442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -15277,12 +15277,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F443" t="inlineStr">
+      <c r="F443" t="inlineStr"/>
+      <c r="G443" t="inlineStr">
         <is>
           <t xml:space="preserve">எப்படி இருக்கிறாய் செல்லம்மா? </t>
         </is>
       </c>
-      <c r="G443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -15310,12 +15310,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F444" t="inlineStr">
+      <c r="F444" t="inlineStr"/>
+      <c r="G444" t="inlineStr">
         <is>
           <t xml:space="preserve">சூறைக்காற்று வீசுது </t>
         </is>
       </c>
-      <c r="G444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -15343,12 +15343,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F445" t="inlineStr">
+      <c r="F445" t="inlineStr"/>
+      <c r="G445" t="inlineStr">
         <is>
           <t xml:space="preserve">செல்லம்மா! எனக்கு? </t>
         </is>
       </c>
-      <c r="G445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -15376,12 +15376,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F446" t="inlineStr">
+      <c r="F446" t="inlineStr"/>
+      <c r="G446" t="inlineStr">
         <is>
           <t xml:space="preserve">பழமொழிக்கிளி! எனக்கு மாங்காய் இல்லையா? </t>
         </is>
       </c>
-      <c r="G446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -15409,12 +15409,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F447" t="inlineStr">
+      <c r="F447" t="inlineStr"/>
+      <c r="G447" t="inlineStr">
         <is>
           <t xml:space="preserve">அகல உழுவதை விட ஆழ உழுவதே மேல் </t>
         </is>
       </c>
-      <c r="G447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -15442,12 +15442,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F448" t="inlineStr">
+      <c r="F448" t="inlineStr"/>
+      <c r="G448" t="inlineStr">
         <is>
           <t xml:space="preserve">மிக்க மகிழ்ச்சி! இதோ உனக்கு மாங்காய், பெற்றுக்கொள். </t>
         </is>
       </c>
-      <c r="G448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -15475,12 +15475,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F449" t="inlineStr">
+      <c r="F449" t="inlineStr"/>
+      <c r="G449" t="inlineStr">
         <is>
           <t xml:space="preserve">ரொம்ப நன்றி பழமொழிக் கிளி! </t>
         </is>
       </c>
-      <c r="G449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -15508,12 +15508,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F450" t="inlineStr">
+      <c r="F450" t="inlineStr"/>
+      <c r="G450" t="inlineStr">
         <is>
           <t xml:space="preserve">காகம் கரைந்து தன் நண்பனான மானைத் தேடியபடி அழைத்தது </t>
         </is>
       </c>
-      <c r="G450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -15541,12 +15541,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F451" t="inlineStr">
+      <c r="F451" t="inlineStr"/>
+      <c r="G451" t="inlineStr">
         <is>
           <t xml:space="preserve">மான் : ஏதோ இருக்கிறேன் நண்பா ........ </t>
         </is>
       </c>
-      <c r="G451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -15574,12 +15574,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F452" t="inlineStr">
+      <c r="F452" t="inlineStr"/>
+      <c r="G452" t="inlineStr">
         <is>
           <t xml:space="preserve">காகம் : குரலில் உற்சாகமில்லையே..... ஏன் சோர்வாகப் பேசுகிறாய்? </t>
         </is>
       </c>
-      <c r="G452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -15607,12 +15607,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F453" t="inlineStr">
+      <c r="F453" t="inlineStr"/>
+      <c r="G453" t="inlineStr">
         <is>
           <t xml:space="preserve">காகம் : என்னோடு வா. உனக்குப் புல் உள்ள இடங்களை காட்டுகிறேன். அங்கு நீ வயிறாரப் புல்லை மேயலாம். </t>
         </is>
       </c>
-      <c r="G453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -15640,12 +15640,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F454" t="inlineStr">
+      <c r="F454" t="inlineStr"/>
+      <c r="G454" t="inlineStr">
         <is>
           <t xml:space="preserve">காகம் : கண்ணால் காண்பதும் பொய். </t>
         </is>
       </c>
-      <c r="G454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -15673,12 +15673,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F455" t="inlineStr">
+      <c r="F455" t="inlineStr"/>
+      <c r="G455" t="inlineStr">
         <is>
           <t xml:space="preserve">காதால் கேட்பதும் பொய். </t>
         </is>
       </c>
-      <c r="G455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -15706,12 +15706,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F456" t="inlineStr">
+      <c r="F456" t="inlineStr"/>
+      <c r="G456" t="inlineStr">
         <is>
           <t xml:space="preserve">செயப்படுபொருள் </t>
         </is>
       </c>
-      <c r="G456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -15739,12 +15739,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F457" t="inlineStr">
+      <c r="F457" t="inlineStr"/>
+      <c r="G457" t="inlineStr">
         <is>
           <t xml:space="preserve">ஒரு தொடரில் யாரை, எதனை, எவற்றை என்னும் வினாக்களுக்கு விடையாக வரும் சொல்லே செயப்படுபொருள் </t>
         </is>
       </c>
-      <c r="G457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -15772,12 +15772,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F458" t="inlineStr">
+      <c r="F458" t="inlineStr"/>
+      <c r="G458" t="inlineStr">
         <is>
           <t xml:space="preserve">பலவண்ண வானவில் எதனாலே? </t>
         </is>
       </c>
-      <c r="G458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -15805,12 +15805,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F459" t="inlineStr">
+      <c r="F459" t="inlineStr"/>
+      <c r="G459" t="inlineStr">
         <is>
           <t xml:space="preserve">விண்மீன் ஒளிர்வது எதனாலே? </t>
         </is>
       </c>
-      <c r="G459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -15838,12 +15838,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F460" t="inlineStr">
+      <c r="F460" t="inlineStr"/>
+      <c r="G460" t="inlineStr">
         <is>
           <t xml:space="preserve">ரோஜாப்பூ சிவப்பது எதனாலே? </t>
         </is>
       </c>
-      <c r="G460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -15871,12 +15871,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F461" t="inlineStr">
+      <c r="F461" t="inlineStr"/>
+      <c r="G461" t="inlineStr">
         <is>
           <t xml:space="preserve">இலைகள் உதிர்வது எதனாலே? </t>
         </is>
       </c>
-      <c r="G461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -15904,12 +15904,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F462" t="inlineStr">
+      <c r="F462" t="inlineStr"/>
+      <c r="G462" t="inlineStr">
         <is>
           <t xml:space="preserve">பறவைகள் பறப்பது எதனாலே? </t>
         </is>
       </c>
-      <c r="G462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -15937,12 +15937,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F463" t="inlineStr">
+      <c r="F463" t="inlineStr"/>
+      <c r="G463" t="inlineStr">
         <is>
           <t xml:space="preserve">மின்னல் மின்னுவது எதனாலே? </t>
         </is>
       </c>
-      <c r="G463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -15970,12 +15970,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F464" t="inlineStr">
+      <c r="F464" t="inlineStr"/>
+      <c r="G464" t="inlineStr">
         <is>
           <t xml:space="preserve">கடலில் அலைகள் எதனாலே? </t>
         </is>
       </c>
-      <c r="G464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -16003,12 +16003,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F465" t="inlineStr">
+      <c r="F465" t="inlineStr"/>
+      <c r="G465" t="inlineStr">
         <is>
           <t xml:space="preserve">மேகம் கறுப்பது எதனாலே? </t>
         </is>
       </c>
-      <c r="G465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -16036,12 +16036,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F466" t="inlineStr">
+      <c r="F466" t="inlineStr"/>
+      <c r="G466" t="inlineStr">
         <is>
           <t xml:space="preserve">அனைத்தின் காரணம் கண்டறிந்தால் </t>
         </is>
       </c>
-      <c r="G466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -16069,12 +16069,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F467" t="inlineStr">
+      <c r="F467" t="inlineStr"/>
+      <c r="G467" t="inlineStr">
         <is>
           <t xml:space="preserve">எதனாலே, எதனாலே? </t>
         </is>
       </c>
-      <c r="G467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -16102,12 +16102,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F468" t="inlineStr">
+      <c r="F468" t="inlineStr"/>
+      <c r="G468" t="inlineStr">
         <is>
           <t xml:space="preserve">முதன்முதலில் அறிவு என்னும் கருவி செயல்படத் தொடங்கிய நாள், மனிதனுக்கு அச்சம் மிகுந்ததாகவே இருந்திருக்கும். தன் அறிவைக் கொண்டு, அவன் சுற்றும் முற்றும் பார்த்தான். காலையில் ஒளிவீசிக் கொண்டிருந்த கதிரவன், திடீரென மாலையில் மறைந்ததும் அவனது அறிவு விழித்துக் கொண்டது. அந்தக் கதிரவன் எங்கேபோனான்? இப்படியே இருளாகத்தான் இருக்குமா? என்று அவன் எண்ணிக் கொண்டிருக்க மறுநாள் மீண்டும் கதிரவன் தோன்றினான். அப்போதே மனிதனின் அறிவு வேலை செய்யத் தொடங்கியது. </t>
         </is>
       </c>
-      <c r="G468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -16135,12 +16135,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F469" t="inlineStr">
+      <c r="F469" t="inlineStr"/>
+      <c r="G469" t="inlineStr">
         <is>
           <t xml:space="preserve">நானும் பறக்கப் போகிறேன் </t>
         </is>
       </c>
-      <c r="G469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -16168,12 +16168,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F470" t="inlineStr">
+      <c r="F470" t="inlineStr"/>
+      <c r="G470" t="inlineStr">
         <is>
           <t xml:space="preserve">அமுதா:ஆமாம்..அப்பா . </t>
         </is>
       </c>
-      <c r="G470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -16201,12 +16201,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F471" t="inlineStr">
+      <c r="F471" t="inlineStr"/>
+      <c r="G471" t="inlineStr">
         <is>
           <t xml:space="preserve">அமுதா:அருமை. இயற்கையைப் பார்த்து வியப்பது, விளையாடுவது இவற்றிலிருந்துகூட நம்மால் நிறைய கற்றுக்கொள்ள முடியுமா? </t>
         </is>
       </c>
-      <c r="G471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -16234,12 +16234,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F472" t="inlineStr">
+      <c r="F472" t="inlineStr"/>
+      <c r="G472" t="inlineStr">
         <is>
           <t xml:space="preserve">நீங்கள் படித்த செய்தி, என்ன வடிவத்தில் உள்ளது? </t>
         </is>
       </c>
-      <c r="G472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -16267,12 +16267,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F473" t="inlineStr">
+      <c r="F473" t="inlineStr"/>
+      <c r="G473" t="inlineStr">
         <is>
           <t xml:space="preserve">படர்க்கை - அவன், அவள், அவர், அது, அவை </t>
         </is>
       </c>
-      <c r="G473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -16300,12 +16300,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F474" t="inlineStr">
+      <c r="F474" t="inlineStr"/>
+      <c r="G474" t="inlineStr">
         <is>
           <t xml:space="preserve">தமிழர்களின் வீரக்கலைகள் </t>
         </is>
       </c>
-      <c r="G474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -16333,12 +16333,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F475" t="inlineStr">
+      <c r="F475" t="inlineStr"/>
+      <c r="G475" t="inlineStr">
         <is>
           <t xml:space="preserve">ஏறுதழுவுதல் </t>
         </is>
       </c>
-      <c r="G475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -16366,12 +16366,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F476" t="inlineStr">
+      <c r="F476" t="inlineStr"/>
+      <c r="G476" t="inlineStr">
         <is>
           <t xml:space="preserve">தனக்கென்று தனித்த நாகரிகமும் பண்பாடும் உடையது தமிழ் மரபு. தமிழரின் பண்பாட்டுக் கூறுகளும் கலைகளும் இலக்கியங்கள் வாயிலாக வெளிப்படுத்தப்பட்டுள்ளன. </t>
         </is>
       </c>
-      <c r="G476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -16399,12 +16399,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F477" t="inlineStr">
+      <c r="F477" t="inlineStr"/>
+      <c r="G477" t="inlineStr">
         <is>
           <t xml:space="preserve">சிலம்பாட்டம் </t>
         </is>
       </c>
-      <c r="G477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -16432,12 +16432,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F478" t="inlineStr">
+      <c r="F478" t="inlineStr"/>
+      <c r="G478" t="inlineStr">
         <is>
           <t xml:space="preserve">தமிழர்களின் மற்றொரு வீர விளையாட்டு, சிலம்பம். சிலம்பு என்றால் ஒலித்தல் என்பது பொருள். கம்பு சுழலும்போது ஏற்படும் ஓசையைஅடிப்படையாகக்கொண்டே சிலம்பம் எனப் பெயரிட்டனர். கம்பு சுழற்றுதல் என்னும் பெயரும் இதற்கு உண்டு. தற்காப்புக்காகத் தோன்றிய இக்கலை, இன்று வீர விளையாட்டாக அறியப்படுகிறது. </t>
         </is>
       </c>
-      <c r="G478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -16465,12 +16465,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F479" t="inlineStr">
+      <c r="F479" t="inlineStr"/>
+      <c r="G479" t="inlineStr">
         <is>
           <t xml:space="preserve">வில்வித்தை  </t>
         </is>
       </c>
-      <c r="G479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -16498,12 +16498,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F480" t="inlineStr">
+      <c r="F480" t="inlineStr"/>
+      <c r="G480" t="inlineStr">
         <is>
           <t xml:space="preserve">மற்போர் </t>
         </is>
       </c>
-      <c r="G480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -16531,12 +16531,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F481" t="inlineStr">
+      <c r="F481" t="inlineStr"/>
+      <c r="G481" t="inlineStr">
         <is>
           <t xml:space="preserve">வித்தை என்பது, வியப்படையச் செய்யும் வகையில் நிகழ்த்தப்படும் ஒரு செயல். அவற்றுள் வில் வித்தையும் ஒன்று. பண்டைத் தமிழர் விரும்பிக் கற்றுக்கொண்ட விளையாட்டாக வில்வித்தை விளங்கியது. தொடக்கத்தில்அம்பெய்தி விலங்குகளை வேட்டையாடவும், போர்முனைகளில் எதிரிகளை வெல்லவும் இவ்வில்லாற்றல் பயன்பட்டது. </t>
         </is>
       </c>
-      <c r="G481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -16564,12 +16564,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F482" t="inlineStr">
+      <c r="F482" t="inlineStr"/>
+      <c r="G482" t="inlineStr">
         <is>
           <t xml:space="preserve">படைக்கலன்கள் ஏதுமின்றி இருவர் போரிடும் விளையாட்டே மற்போர். மல் என்பது, வலிமையைக் குறிக்கும். ஒருவன் தன் உடல் வலிமையால் செய்யும் போரே, ‘மற்போர்‘. மற்போரில்வெற்றி பெற்றவர்களை ‘மல்லன்‘ என்னும் சொல்லால் குறிக்கும் வழக்கம் இருந்தது. மற்போரில் சிறந்து விளங்கியமையாலேயே மாமல்லன் என்று அக்கால அரசர்கள் போற்றப்பெற்றனர். </t>
         </is>
       </c>
-      <c r="G482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -16597,12 +16597,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F483" t="inlineStr">
+      <c r="F483" t="inlineStr"/>
+      <c r="G483" t="inlineStr">
         <is>
           <t xml:space="preserve">கங்கை கொண்ட சோழபுரம் </t>
         </is>
       </c>
-      <c r="G483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -16630,12 +16630,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F484" t="inlineStr">
+      <c r="F484" t="inlineStr"/>
+      <c r="G484" t="inlineStr">
         <is>
           <t xml:space="preserve">கங்கை கொண்டான் மண்ணெடுத்து </t>
         </is>
       </c>
-      <c r="G484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -16663,12 +16663,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F485" t="inlineStr">
+      <c r="F485" t="inlineStr"/>
+      <c r="G485" t="inlineStr">
         <is>
           <t xml:space="preserve">ஆறு சட்டம் நூறு பண்ணி </t>
         </is>
       </c>
-      <c r="G485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -16696,12 +16696,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F486" t="inlineStr">
+      <c r="F486" t="inlineStr"/>
+      <c r="G486" t="inlineStr">
         <is>
           <t xml:space="preserve">கயலினி மகிழ்ச்சியில் துள்ளிக் குதித்தாள். ஏன்? இந்த விடுமுறை நாள்களை அவள் மகிழ்வுடன் கழிக்கப் போகிறாள் அல்லவா! அதனால்தான். அன்பு தரும் ஆசைப் பாட்டியின் ஊருக்குப் புறப்படத் தயாராகிவிட்டாள். வாருங்கள், குழந்தைகளே! நாமும் அவள் மகிழ்ச்சியில் பங்கெடுத்துக் கொள்வோம். </t>
         </is>
       </c>
-      <c r="G486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -16729,12 +16729,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F487" t="inlineStr">
+      <c r="F487" t="inlineStr"/>
+      <c r="G487" t="inlineStr">
         <is>
           <t xml:space="preserve">சிறிது ஓய்வுக்குப் பிறகு மீண்டும், ‘பாட்டி…’ என்று இழுத்தாள் கயலினி.” சரி…சரி.. நான் புரிந்து கொண்டேன் வா போகலாம்” என்று பாட்டி கூற இருவரும் சோழ நாட்டுக்கு வளம் சேர்த்த சோழ கங்கத்தை அடைந்தனர். ‘இதுதான் சோழ கங்கம். பார்த்தாயா இதன் அழகை!’ என்று பாட்டி சொல்லி முடிக்கவில்லை. அதற்குள் கயலினி, “பாட்டி, இது என்ன பொன்னேரினு எழுதியிருக்கு? நீங்க சோழ கங்கம்னு சொல்றீங்க?” எனக் கேட்டாள். </t>
         </is>
       </c>
-      <c r="G487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -16762,12 +16762,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F488" t="inlineStr">
+      <c r="F488" t="inlineStr"/>
+      <c r="G488" t="inlineStr">
         <is>
           <t xml:space="preserve">கலையழகும் புதுப்பொலிவும் கொண்ட சிற்பக் கூடமாகவே கங்கை கொண்ட சோழபுரம் அமைந்துள்ளது. யுனெஸ்கோ நிறுவனம் உலகப் பாரம்பரியச் சின்னமாகக் கங்கை கொண்ட சோழபுரத்தை அறிவித்துள்ளது நமக்கெல்லாம் பெருமைதானே! </t>
         </is>
       </c>
-      <c r="G488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -16795,12 +16795,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F489" t="inlineStr">
+      <c r="F489" t="inlineStr"/>
+      <c r="G489" t="inlineStr">
         <is>
           <t xml:space="preserve">இணைப்புச்சொற்கள் </t>
         </is>
       </c>
-      <c r="G489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -16828,12 +16828,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F490" t="inlineStr">
+      <c r="F490" t="inlineStr"/>
+      <c r="G490" t="inlineStr">
         <is>
           <t xml:space="preserve">செழியன் : இளந்தமிழா, நாளை வெளியூர் செல்வதாகக் கூறினாயே? மறந்துவிட்டாயா? உன்னுடன் யாரெல்லாம் வருகிறார்கள்? </t>
         </is>
       </c>
-      <c r="G490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -16861,12 +16861,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F491" t="inlineStr">
+      <c r="F491" t="inlineStr"/>
+      <c r="G491" t="inlineStr">
         <is>
           <t xml:space="preserve">செழியன் : அப்படியானால் நீ கவனமாக இருக்கவேண்டும் அல்லவா? </t>
         </is>
       </c>
-      <c r="G491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -16894,12 +16894,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F492" t="inlineStr">
+      <c r="F492" t="inlineStr"/>
+      <c r="G492" t="inlineStr">
         <is>
           <t xml:space="preserve">இளந்தமிழ் : மறக்கவில்லை, செழியா! நாளை நான் மட்டும்தான் செல்வதாக இருக்கிறேன். அதனால், என்னுடன் யாரும் வரவில்லை. </t>
         </is>
       </c>
-      <c r="G492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -16927,12 +16927,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F493" t="inlineStr">
+      <c r="F493" t="inlineStr"/>
+      <c r="G493" t="inlineStr">
         <is>
           <t xml:space="preserve">இளந்தமிழ் : நான் ஏற்கெனவேசென்றஇடம்தான். ஆதலால், அச்சம் ஒன்றும் இல்லை. </t>
         </is>
       </c>
-      <c r="G493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -16960,12 +16960,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F494" t="inlineStr">
+      <c r="F494" t="inlineStr"/>
+      <c r="G494" t="inlineStr">
         <is>
           <t xml:space="preserve">செழியன் : ஏனெனில், இந்த வார இறுதியில், நமக்கு மட்டைப்பந்து போட்டி இருக்கிறது. அதனால்தான் கேட்கிறேன். நீ கட்டாயம் கலந்துகொள்ள வேண்டும். ஆகவே, மறந்துவிடாதே நண்பா! </t>
         </is>
       </c>
-      <c r="G494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -16993,12 +16993,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F495" t="inlineStr">
+      <c r="F495" t="inlineStr"/>
+      <c r="G495" t="inlineStr">
         <is>
           <t xml:space="preserve">புதுவனம் நிறைந்தறம் தங்குகவே </t>
         </is>
       </c>
-      <c r="G495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -17026,12 +17026,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F496" t="inlineStr">
+      <c r="F496" t="inlineStr"/>
+      <c r="G496" t="inlineStr">
         <is>
           <t xml:space="preserve">எங்கணும் யாவரும் இன்பமுற </t>
         </is>
       </c>
-      <c r="G496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -17059,12 +17059,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F497" t="inlineStr">
+      <c r="F497" t="inlineStr"/>
+      <c r="G497" t="inlineStr">
         <is>
           <t xml:space="preserve">ஏர்த்தொழில் ஒன்றே தெம்புதரும் </t>
         </is>
       </c>
-      <c r="G497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -17092,12 +17092,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F498" t="inlineStr">
+      <c r="F498" t="inlineStr"/>
+      <c r="G498" t="inlineStr">
         <is>
           <t xml:space="preserve">பொங்குக பொங்கல் பொங்குகவே </t>
         </is>
       </c>
-      <c r="G498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -17125,12 +17125,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F499" t="inlineStr">
+      <c r="F499" t="inlineStr"/>
+      <c r="G499" t="inlineStr">
         <is>
           <t xml:space="preserve">உணவுப் பொருள்கள் இல்லாமல் </t>
         </is>
       </c>
-      <c r="G499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -17158,12 +17158,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F500" t="inlineStr">
+      <c r="F500" t="inlineStr"/>
+      <c r="G500" t="inlineStr">
         <is>
           <t xml:space="preserve">உயிரோ டிருப்பது செல்லாது </t>
         </is>
       </c>
-      <c r="G500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -17191,12 +17191,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F501" t="inlineStr">
+      <c r="F501" t="inlineStr"/>
+      <c r="G501" t="inlineStr">
         <is>
           <t xml:space="preserve">பணமும் அதுதரும் நலனெல்லாம் </t>
         </is>
       </c>
-      <c r="G501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -17224,12 +17224,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F502" t="inlineStr">
+      <c r="F502" t="inlineStr"/>
+      <c r="G502" t="inlineStr">
         <is>
           <t xml:space="preserve">உழவுத் தொழில்தான் உணவுதரும் </t>
         </is>
       </c>
-      <c r="G502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -17257,12 +17257,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F503" t="inlineStr">
+      <c r="F503" t="inlineStr"/>
+      <c r="G503" t="inlineStr">
         <is>
           <t xml:space="preserve">பழகும் மற்றுள தொழில்யாவும் </t>
         </is>
       </c>
-      <c r="G503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -17290,12 +17290,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F504" t="inlineStr">
+      <c r="F504" t="inlineStr"/>
+      <c r="G504" t="inlineStr">
         <is>
           <t xml:space="preserve">தானியம் ஒன்றே விருந்தாகும் </t>
         </is>
       </c>
-      <c r="G504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -17323,12 +17323,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F505" t="inlineStr">
+      <c r="F505" t="inlineStr"/>
+      <c r="G505" t="inlineStr">
         <is>
           <t xml:space="preserve">தங்கமும் வெள்ளியும் இருந்தாலும் </t>
         </is>
       </c>
-      <c r="G505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -17356,12 +17356,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F506" t="inlineStr">
+      <c r="F506" t="inlineStr"/>
+      <c r="G506" t="inlineStr">
         <is>
           <t xml:space="preserve">இங்கிதன் உண்மையை உணர்ந்திடுவோம் </t>
         </is>
       </c>
-      <c r="G506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -17389,12 +17389,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F507" t="inlineStr">
+      <c r="F507" t="inlineStr"/>
+      <c r="G507" t="inlineStr">
         <is>
           <t xml:space="preserve">உழவே செல்வம் உண்டுபண்ணும் </t>
         </is>
       </c>
-      <c r="G507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -17422,12 +17422,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F508" t="inlineStr">
+      <c r="F508" t="inlineStr"/>
+      <c r="G508" t="inlineStr">
         <is>
           <t xml:space="preserve">உழைப்பே இன்பம் கொண்டுவரும் </t>
         </is>
       </c>
-      <c r="G508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -17455,12 +17455,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F509" t="inlineStr">
+      <c r="F509" t="inlineStr"/>
+      <c r="G509" t="inlineStr">
         <is>
           <t xml:space="preserve">உற்றஇப் பொங்கல் திருநாளாம் </t>
         </is>
       </c>
-      <c r="G509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -17488,12 +17488,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F510" t="inlineStr">
+      <c r="F510" t="inlineStr"/>
+      <c r="G510" t="inlineStr">
         <is>
           <t xml:space="preserve">ஏழையும் செல்வரும் இங்கிதமாய் </t>
         </is>
       </c>
-      <c r="G510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -17521,12 +17521,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F511" t="inlineStr">
+      <c r="F511" t="inlineStr"/>
+      <c r="G511" t="inlineStr">
         <is>
           <t xml:space="preserve">இசைந்துளம் களித்திடும் பொங்கலிது </t>
         </is>
       </c>
-      <c r="G511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -17554,12 +17554,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F512" t="inlineStr">
+      <c r="F512" t="inlineStr"/>
+      <c r="G512" t="inlineStr">
         <is>
           <t xml:space="preserve">வாழிய பயிர்த்தொழில் வளம்பெருகி </t>
         </is>
       </c>
-      <c r="G512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -17587,12 +17587,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F513" t="inlineStr">
+      <c r="F513" t="inlineStr"/>
+      <c r="G513" t="inlineStr">
         <is>
           <t xml:space="preserve"> நாமக்கல் வெ. இராமலிங்கனார்</t>
         </is>
       </c>
-      <c r="G513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -17620,12 +17620,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F514" t="inlineStr">
+      <c r="F514" t="inlineStr"/>
+      <c r="G514" t="inlineStr">
         <is>
           <t xml:space="preserve">பாரதி: ஐயா! அங்கே பாருங்கள். இயற்கை உணவுப்பொருள்கள் என்று எழுதப்பட்ட அந்த அரங்கத்தில் எல்லாரும் ஏதோ சுவைக்கிறார்கள். நாமும் அங்கே செல்லலாமா? </t>
         </is>
       </c>
-      <c r="G514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -17653,12 +17653,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F515" t="inlineStr">
+      <c r="F515" t="inlineStr"/>
+      <c r="G515" t="inlineStr">
         <is>
           <t xml:space="preserve">ஆசிரியர்களுடன் மாணவர்களும் அந்த அரங்கில் நுழைந்தார்கள். இயற்கை உணவுகளைச் சுவைத்து மகிழ்ந்தார்கள். </t>
         </is>
       </c>
-      <c r="G515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -17686,12 +17686,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F516" t="inlineStr">
+      <c r="F516" t="inlineStr"/>
+      <c r="G516" t="inlineStr">
         <is>
           <t xml:space="preserve">மணிமொழி: விழாவிற்கு வந்தவர்களுக்கு இயற்கை முறையில் தயாரித்த நவதானிய உணவுகளான இனிப்பு உருண்டை, பிட்டு, பொங்கல், கேழ்வரகுக் கூழ், கேழ்வரகு அடை, முளைகட்டிய பாசிப்பயறு, நவதானிய சுண்டல். கொண்டைக்கடலை, தட்டைப்பயறு, மொச்சை போன்ற தின்பொருள்களை வழங்குகிறார்கள் </t>
         </is>
       </c>
-      <c r="G516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -17719,12 +17719,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F517" t="inlineStr">
+      <c r="F517" t="inlineStr"/>
+      <c r="G517" t="inlineStr">
         <is>
           <t xml:space="preserve">பல ஆண்டுகளுக்குமுன் தென் பாண்டிய நாட்டை மங்கையர்க்கரசி என்பவர் ஆண்டு வந்தார். அவர், நீதியும் நேர்மையும் மிக்கவராக விளங்கினார். அவர் ஆட்சியில் மக்கள் குறைவின்றி வாழ்ந்து வந்தனர். </t>
         </is>
       </c>
-      <c r="G517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -17752,12 +17752,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F518" t="inlineStr">
+      <c r="F518" t="inlineStr"/>
+      <c r="G518" t="inlineStr">
         <is>
           <t xml:space="preserve">நான்காவதாக முதியவர் ஒருவர் வந்தார். அவர், தமது சாதனை என்ன என்று சொல்லலானார். “நான் சாதாரண ஓர் ஏழை விவசாயி. என் மூதாதையர் வழியில் எனக்குக் கிடைத்த ஒரு காணி நிலத்தை நன்கு உழுது பயிரிட்டுப் பிழைத்து வருகிறேன். என் மனைவி காலமாகிவிட்டாள். என் மகளும் நானும்தான் வயலில் உழைத்து வாழ்க்கை நடத்துகிறோம். இருவரும் பாடுபட்டு வேலை செய்ததால், கடந்த ஆண்டைவிட இந்த ஆண்டு மூன்று மடங்கு விளைச்சல் கண்டுள்ளது. என் குடும்பத்திற்குத் தேவையான நெல் போக, மீதியைப் பத்துக் குடும்பத்திற்கு விற்றேன். ஒரு காணி நிலத்தைக் கொண்டு பத்துக் குடும்பத்தைக் காப்பாற்றியது என் சாதனைதானே?” என்று கேட்டார் முதியவர். </t>
         </is>
       </c>
-      <c r="G518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -17785,12 +17785,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F519" t="inlineStr">
+      <c r="F519" t="inlineStr"/>
+      <c r="G519" t="inlineStr">
         <is>
           <t xml:space="preserve">பாணன்: ஆம்! நானும் கேள்விப்பட்டுள்ளேன். வீரத்திலும் கொடைத் திறத்திலும் சிறந்தவர். இப்பொழுதே செல்கிறேன். </t>
         </is>
       </c>
-      <c r="G519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -17818,12 +17818,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F520" t="inlineStr">
+      <c r="F520" t="inlineStr"/>
+      <c r="G520" t="inlineStr">
         <is>
           <t>பாணன்:  கொல்லிமலைக் கொற்றவா! கொடைத் திறத்தின் கோமகனே! நீவிர் வாழ்க! உமது படை வாழ்க!</t>
         </is>
       </c>
-      <c r="G520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -17851,12 +17851,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F521" t="inlineStr">
+      <c r="F521" t="inlineStr"/>
+      <c r="G521" t="inlineStr">
         <is>
           <t>பாணன்:  உணவின்றி என் இல்லாள் மெலிந்து கிடக்கிறாள். பிள்ளைகளோ காற்றை உண்டு கண்ணில் உயிரைத் தேக்கியபடி இருக்கின்றனர்</t>
         </is>
       </c>
-      <c r="G521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -17884,12 +17884,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F522" t="inlineStr">
+      <c r="F522" t="inlineStr"/>
+      <c r="G522" t="inlineStr">
         <is>
           <t xml:space="preserve">மூன்றாவது போட்டி மக்களிடம் பரிவு காட்டவேண்டும் என்பதாகும். அதனை ஒப்புக்கொண்டு இருவரும் சென்றனர். மறுநாள் பாலன் சிந்தித்துக் கொண்டே நடந்து சென்றார். அவ்வழியில் மூதாட்டி ஒருவர் மரத்தடியில் படுத்திருந்தார். “தம்பி, என்னைத் தூக்கிவிடு, என்னால் எழுந்திருக்க முடியவில்லை“ என்றார். ''எனக்கு அவசர வேலை இருக்கிறது'' என்று கூறிக்கொண்டே பாலன் வேகமாகச் சென்றுவிட்டார். </t>
         </is>
       </c>
-      <c r="G522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -17917,12 +17917,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F523" t="inlineStr">
+      <c r="F523" t="inlineStr"/>
+      <c r="G523" t="inlineStr">
         <is>
           <t xml:space="preserve">நன்மையும் மென்மையும் தோன்றும் – நல </t>
         </is>
       </c>
-      <c r="G523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -17950,12 +17950,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F524" t="inlineStr">
+      <c r="F524" t="inlineStr"/>
+      <c r="G524" t="inlineStr">
         <is>
           <t xml:space="preserve">நயமதும் நம்மை அண்டும் </t>
         </is>
       </c>
-      <c r="G524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -17983,12 +17983,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F525" t="inlineStr">
+      <c r="F525" t="inlineStr"/>
+      <c r="G525" t="inlineStr">
         <is>
           <t xml:space="preserve">வளமதை எட்டிட வேண்டும் </t>
         </is>
       </c>
-      <c r="G525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -18016,12 +18016,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F526" t="inlineStr">
+      <c r="F526" t="inlineStr"/>
+      <c r="G526" t="inlineStr">
         <is>
           <t xml:space="preserve">கல்வியைக் கற்றிட வேண்டும் – அதைக் </t>
         </is>
       </c>
-      <c r="G526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -18049,12 +18049,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F527" t="inlineStr">
+      <c r="F527" t="inlineStr"/>
+      <c r="G527" t="inlineStr">
         <is>
           <t xml:space="preserve">வல்லமை பெற்றிட வேண்டும் – நல்  </t>
         </is>
       </c>
-      <c r="G527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -18082,12 +18082,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F528" t="inlineStr">
+      <c r="F528" t="inlineStr"/>
+      <c r="G528" t="inlineStr">
         <is>
           <t xml:space="preserve">வெளிச்சமும் மேனியில் ஊறும் </t>
         </is>
       </c>
-      <c r="G528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -18115,12 +18115,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F529" t="inlineStr">
+      <c r="F529" t="inlineStr"/>
+      <c r="G529" t="inlineStr">
         <is>
           <t xml:space="preserve">கற்றிடக் கற்றிட யாவும் – நல் </t>
         </is>
       </c>
-      <c r="G529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -18148,12 +18148,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F530" t="inlineStr">
+      <c r="F530" t="inlineStr"/>
+      <c r="G530" t="inlineStr">
         <is>
           <t xml:space="preserve">வெற்றிகள் ஆயிரம் சேரும் – புகழ் </t>
         </is>
       </c>
-      <c r="G530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -18181,12 +18181,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F531" t="inlineStr">
+      <c r="F531" t="inlineStr"/>
+      <c r="G531" t="inlineStr">
         <is>
           <t xml:space="preserve">விண்ணையும் அளந்திட வைக்கும் – நம்மை </t>
         </is>
       </c>
-      <c r="G531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -18214,12 +18214,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F532" t="inlineStr">
+      <c r="F532" t="inlineStr"/>
+      <c r="G532" t="inlineStr">
         <is>
           <t xml:space="preserve">விடியலாய் எழுந்திட வைக்கும் </t>
         </is>
       </c>
-      <c r="G532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -18247,12 +18247,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F533" t="inlineStr">
+      <c r="F533" t="inlineStr"/>
+      <c r="G533" t="inlineStr">
         <is>
           <t xml:space="preserve"> - பாரதிசுகுமாரன்</t>
         </is>
       </c>
-      <c r="G533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -18280,12 +18280,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F534" t="inlineStr">
+      <c r="F534" t="inlineStr"/>
+      <c r="G534" t="inlineStr">
         <is>
           <t xml:space="preserve">வாயிற்காப்போன்: கேட்டேன், மன்னவா! அதைப்பற்றி உங்களிடம்தான் கூறவேண்டும் என்று சொல்கிறாள். அவள் உங்களிடம் நீதி கேட்டு வந்திருப்பதாகக் கூறுகிறாள். </t>
         </is>
       </c>
-      <c r="G534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -18313,12 +18313,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F535" t="inlineStr">
+      <c r="F535" t="inlineStr"/>
+      <c r="G535" t="inlineStr">
         <is>
           <t xml:space="preserve">பாண்டிய மன்னர், தாம் தவறாக வழங்கிய தீர்ப்பால் உண்டான பழிச்சொல்லுக்கு அஞ்சி, அரியணையிலிருந்து தரைமீது வீழ்ந்து, இறந்துபடுகிறார். </t>
         </is>
       </c>
-      <c r="G535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -18346,12 +18346,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F536" t="inlineStr">
+      <c r="F536" t="inlineStr"/>
+      <c r="G536" t="inlineStr">
         <is>
           <t xml:space="preserve">﻿அவன் சென்றபின், “பணத்தை வைத்திருப்பவன் மட்டுமே பணக்காரன் அல்லன்; சொன்ன சொல்லை மறவாது மற்றவர்க்குப் பெருந்தன்மையுடன் கொடுக்கும் உள்ளம் படைத்தவனே பணக்காரன்” என்று கூறிய அரசன், மூதாட்டியின் நேர்மையைப் பாராட்டிப் பணப்பையை அவருக்கே பரிசாகவும் கொடுத்துவிட்டான். </t>
         </is>
       </c>
-      <c r="G536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -18379,12 +18379,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F537" t="inlineStr">
+      <c r="F537" t="inlineStr"/>
+      <c r="G537" t="inlineStr">
         <is>
           <t xml:space="preserve">நீதி : ‘நேர்மை நன்மை தரும்’ </t>
         </is>
       </c>
-      <c r="G537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -18412,12 +18412,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F538" t="inlineStr">
+      <c r="F538" t="inlineStr"/>
+      <c r="G538" t="inlineStr">
         <is>
           <t xml:space="preserve">அப்பா ஆமாம், யாழினி. ஆசிரியர் கூறுவதை நீ நன்கு உற்றுக் கவனித்திருக்கிறாய். பாராட்டுகள். பாரதிதாசனுக்கு அவர் பெற்றோர் இட்டபெயர் கனகசுப்புரத்தினம். இளமையிலேயே கவிபாடும் ஆற்றல் கொண்டிருந்தார். பாரதியார்முன் ‘எங்கெங்கு காணினும் சக்தியடா!’ என்ற பாடலைப் பாடிக்காட்டினார். பாரதியார் மீது அன்பும் பாசமும், பற்றும் உடையவர். அதனால்தான், த பெயரைப் பாரதிதாசன் என்று மாற்றியமைத்துக்கொண்டார். </t>
         </is>
       </c>
-      <c r="G538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -18445,12 +18445,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F539" t="inlineStr">
+      <c r="F539" t="inlineStr"/>
+      <c r="G539" t="inlineStr">
         <is>
           <t xml:space="preserve">யாழினி அப்பா, அங்கே பாருங்கள். பக்கத்து வீட்டு பூங்குழலி! </t>
         </is>
       </c>
-      <c r="G539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -18478,12 +18478,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F540" t="inlineStr">
+      <c r="F540" t="inlineStr"/>
+      <c r="G540" t="inlineStr">
         <is>
           <t xml:space="preserve"> அப்பா ஆம். 33 நாடகங்களுக்குமேல் எழுதியுள்ளார். பூங்குழலி வாசிக்க விரும்பும் ‘பிசிராந்தையார்’ நாடக நூல் “சாகித்திய அகாதெமி” விருது பெற்றுள்ளது</t>
         </is>
       </c>
-      <c r="G540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -18511,12 +18511,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F541" t="inlineStr">
+      <c r="F541" t="inlineStr"/>
+      <c r="G541" t="inlineStr">
         <is>
           <t xml:space="preserve">யாழினி அப்பா கேட்கவே மகிழ்வாக இருக்கிறது. </t>
         </is>
       </c>
-      <c r="G541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -18544,12 +18544,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F542" t="inlineStr">
+      <c r="F542" t="inlineStr"/>
+      <c r="G542" t="inlineStr">
         <is>
           <t xml:space="preserve">அப்பா ஓ! இருந்தார்களே! தமிழில் பிழையின்றி எழுதுவது குறித்த நூல்களைப் படைத்தவர், இலக்கணச் சுடர் இரா. திருமுருகன். இவர், தனித்தமிழ்ப் பற்றால் சுப்பிரமணியன் என்ற தம் பெயரைத் ‘திருமுருகன்’ என்று மாற்றி அமைத்துக் கொண்டார். </t>
         </is>
       </c>
-      <c r="G542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -18577,12 +18577,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F543" t="inlineStr">
+      <c r="F543" t="inlineStr"/>
+      <c r="G543" t="inlineStr">
         <is>
           <t xml:space="preserve">பூங்குழலி ஆமாம், யாழினி. முத்தமிழ் போற்றும் நம் முன்னோர்களை வணங்குவதோடு அவர்களின் நூல்களையும் நாம் தேடித் தேடிப் படிப்போம். </t>
         </is>
       </c>
-      <c r="G543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -18610,12 +18610,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F544" t="inlineStr">
+      <c r="F544" t="inlineStr"/>
+      <c r="G544" t="inlineStr">
         <is>
           <t xml:space="preserve">தமிழ்மணியின் வீட்டில் அழகிய தோட்டம் ஒன்று இருந்தது. வண்ண வண்ண மலர்களும் பயன் தரும் செடி, கொடிகளும் அங்கு நிறைந்திருந்தன. தோட்டத்தின் அருகிலேயே சில மரங்களும் இருந்தன. அதனால், அந்த இடத்தில் எப்போதும் குளிர்ச்சியும் தூய்மையான காற்றும் இருந்துகொண்டே இருக்கும். </t>
         </is>
       </c>
-      <c r="G544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -18643,12 +18643,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F545" t="inlineStr">
+      <c r="F545" t="inlineStr"/>
+      <c r="G545" t="inlineStr">
         <is>
           <t xml:space="preserve">மாலை மூன்று மணியிலிருந்தே நண்பர்கள் தமிழ்மணியின் வீட்டுக்கு வரத் தொடங்கினர். தோட்டத்தைப் பார்த்ததும் அவர்களுக்குக் கட்டுக்கடங்கா மகிழ்ச்சி ஏற்பட்டது. சிலர் அங்கிருந்த பூக்களைப் பறித்துக் கீழே போட்டனர். சிலர், இலைகளைச் சுருட்டி அடுத்தவர் காதில் ஊதினர். ஊஞ்சலில் ஏறியும் இறங்கியும் சிலர் விளையாடினர். சிலர், மரத்திற்கு மரம் ஓடிப்பிடித்து விளையாடினர். தமிழ்மணியும் அவர்களோடு சேர்ந்து மகிழ்ச்சியாக ஆடிக்கொண்டிருந்தான். </t>
         </is>
       </c>
-      <c r="G545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -18676,12 +18676,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F546" t="inlineStr">
+      <c r="F546" t="inlineStr"/>
+      <c r="G546" t="inlineStr">
         <is>
           <t xml:space="preserve">அச்சமயம், அவன் நண்பன் ரஷீத் மரத்தின் மேலிருந்த பறவைக்கூட்டைப் பார்த்தான். “எல்லாரும் இங்க பாருங்க, சின்னச் சின்னதாப் பறவைக்குஞ்சுகள் இருக்கும்போல, கீச்…கீச்னு சத்தம் கேட்குது“ என்றான் ரஷீத். அங்கங்கே விளையாடிக் கொண்டிருந்த நண்பர்கள் எல்லாம் பறவைக்கூடு இருந்த மரத்தினருகே ஒன்றுகூடினார்கள். </t>
         </is>
       </c>
-      <c r="G546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -18709,12 +18709,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F547" t="inlineStr">
+      <c r="F547" t="inlineStr"/>
+      <c r="G547" t="inlineStr">
         <is>
           <t xml:space="preserve">அப்போது அங்கு வந்த தமிழ்மணியின் பெற்றோர் நடந்ததை அறிந்துகொண்டனர். “நம்மைப்போலத்தான் இவ்வுலகில் எல்லா உயிர்களும் வாழ்கின்றன. </t>
         </is>
       </c>
-      <c r="G547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -18742,12 +18742,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F548" t="inlineStr">
+      <c r="F548" t="inlineStr"/>
+      <c r="G548" t="inlineStr">
         <is>
           <t xml:space="preserve">அவர் கூறியதைப் புரிந்துகொண்ட தமிழ்மணியும் நண்பர்களும் “இனி நாங்கள் யாரையும் துன்புறுத்த மாட்டோம்“ என்று உறுதி கூறினர். தாங்கள் கூறியதை மெய்ப்பிப்பதுபோல், கொண்டு வந்த தின்பண்டங்களையும் சிறுதானியங்களையும் பறவைகளுக்குக் கொடுத்தனர். </t>
         </is>
       </c>
-      <c r="G548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -18775,12 +18775,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F549" t="inlineStr">
+      <c r="F549" t="inlineStr"/>
+      <c r="G549" t="inlineStr">
         <is>
           <t xml:space="preserve">தன்னுடைய இழிவான செயலை நினைத்த பீட்டர், என்னசொல்வதென்று தெரியாமல் தலைகுனிந்து நின்றான். “தமிழ், என்னை மன்னித்துவிடுடா, நான் அறியாமல் செய்த தவற்றை எண்ணி வருந்துகிறேன். இனி எப்போதும் இதுபோன்ற தவறுகளைச் செய்ய மாட்டேன்“ என்று வருத்தத்துடன் கூறினான் பீட்டர். அவன் கூறியதைக் கேட்ட மற்ற நண்பர்கள், “அவன்தான் தவற்றை ஒப்புக்கொண்டானே, மன்னித்துவிடுடா, அவன் மட்டும் இல்லே நாங்களும் இதுபோன்று தவறு செய்யமாட்டோம்“ என்று கூறினர். </t>
         </is>
       </c>
-      <c r="G549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -18808,12 +18808,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F550" t="inlineStr">
+      <c r="F550" t="inlineStr"/>
+      <c r="G550" t="inlineStr">
         <is>
           <t>அன்பான சிங்கம் அது ஓர்அடர்ந்த காடு. அந்தக்காட்டில் சிங்கம் ஒன்று இருந்தது. அது மிகவும் அன்பானது. குகையிலிருந்து வெளியே வந்தது. அப்போது மரத்தின் கீழே பசியோடு  அமர்ந்திருந்த அணிலைக் கண்டது. அருகில் சென்றது. அணில் பயந்து நடுங்கியது. சிங்கமோ அணிலுக்குப்பழம் ஒன்றைக் கொடுத்தது. அணில்அன்புடன் நன்றி கூறியது</t>
         </is>
       </c>
-      <c r="G550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -18841,27 +18841,27 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F551" t="inlineStr">
+      <c r="F551" t="inlineStr"/>
+      <c r="G551" t="inlineStr">
         <is>
           <t>மனம்‌ வருந்தினான்‌. அவர்களுடன்‌ ஓடியாடி  ,</t>
         </is>
       </c>
-      <c r="G551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>660edfc6ee2bf77136b3aedf</t>
+          <t>6647557a2740a348c116e889</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>f3e318a7-9e45-4a12-9f10-2435cce8622b</t>
+          <t>e6e3fa31-2c92-45a4-bc73-e148f9a71946</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>word</t>
+          <t>sentence</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
@@ -18871,34 +18871,30 @@
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>collectionId</t>
-        </is>
-      </c>
-      <c r="F552" t="inlineStr">
-        <is>
-          <t>bd20fee5-31c3-48d9-ab6f-842eeebf17ff</t>
-        </is>
-      </c>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr"/>
       <c r="G552" t="inlineStr">
         <is>
-          <t>e4ab8ac2-38c2-4dcc-83f1-654548629a50</t>
+          <t xml:space="preserve">அவர்களுடன்‌ கபடி, கண்ணாமூச்சி, கயிறு தாண்டுதல்‌, விளையாடியதை எண்ணி ஏங்கினான்‌. </t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>660edfc6ee2bf77136b3aee1</t>
+          <t>664755862740a348c116e8a3</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>0025a873-faff-4d77-a864-a1971dc466e8</t>
+          <t>4b9a8d81-0818-442e-877f-c00387564c09</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>word</t>
+          <t>sentence</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
@@ -18908,751 +18904,15 @@
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>collectionId</t>
-        </is>
-      </c>
-      <c r="F553" t="inlineStr">
-        <is>
-          <t>bd20fee5-31c3-48d9-ab6f-842eeebf17ff</t>
-        </is>
-      </c>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr"/>
       <c r="G553" t="inlineStr">
         <is>
-          <t>e4ab8ac2-38c2-4dcc-83f1-654548629a50</t>
-        </is>
-      </c>
-    </row>
-    <row r="554">
-      <c r="A554" t="inlineStr">
-        <is>
-          <t>660edfc6ee2bf77136b3aee3</t>
-        </is>
-      </c>
-      <c r="B554" t="inlineStr">
-        <is>
-          <t>f634799b-5359-4512-b5a2-03e3c59d6f8b</t>
-        </is>
-      </c>
-      <c r="C554" t="inlineStr">
-        <is>
-          <t>word</t>
-        </is>
-      </c>
-      <c r="D554" t="inlineStr">
-        <is>
-          <t>ta</t>
-        </is>
-      </c>
-      <c r="E554" t="inlineStr">
-        <is>
-          <t>collectionId</t>
-        </is>
-      </c>
-      <c r="F554" t="inlineStr">
-        <is>
-          <t>bd20fee5-31c3-48d9-ab6f-842eeebf17ff</t>
-        </is>
-      </c>
-      <c r="G554" t="inlineStr">
-        <is>
-          <t>e4ab8ac2-38c2-4dcc-83f1-654548629a50</t>
-        </is>
-      </c>
-    </row>
-    <row r="555">
-      <c r="A555" t="inlineStr">
-        <is>
-          <t>660edfc7ee2bf77136b3aee5</t>
-        </is>
-      </c>
-      <c r="B555" t="inlineStr">
-        <is>
-          <t>125730ae-d8b6-4bc5-b13f-3bba8bcdba33</t>
-        </is>
-      </c>
-      <c r="C555" t="inlineStr">
-        <is>
-          <t>word</t>
-        </is>
-      </c>
-      <c r="D555" t="inlineStr">
-        <is>
-          <t>ta</t>
-        </is>
-      </c>
-      <c r="E555" t="inlineStr">
-        <is>
-          <t>collectionId</t>
-        </is>
-      </c>
-      <c r="F555" t="inlineStr">
-        <is>
-          <t>bd20fee5-31c3-48d9-ab6f-842eeebf17ff</t>
-        </is>
-      </c>
-      <c r="G555" t="inlineStr">
-        <is>
-          <t>e4ab8ac2-38c2-4dcc-83f1-654548629a50</t>
-        </is>
-      </c>
-    </row>
-    <row r="556">
-      <c r="A556" t="inlineStr">
-        <is>
-          <t>660edfc7ee2bf77136b3aee9</t>
-        </is>
-      </c>
-      <c r="B556" t="inlineStr">
-        <is>
-          <t>121b59bf-b1e1-442f-b944-433e4998b7da</t>
-        </is>
-      </c>
-      <c r="C556" t="inlineStr">
-        <is>
-          <t>word</t>
-        </is>
-      </c>
-      <c r="D556" t="inlineStr">
-        <is>
-          <t>ta</t>
-        </is>
-      </c>
-      <c r="E556" t="inlineStr">
-        <is>
-          <t>collectionId</t>
-        </is>
-      </c>
-      <c r="F556" t="inlineStr">
-        <is>
-          <t>bd20fee5-31c3-48d9-ab6f-842eeebf17ff</t>
-        </is>
-      </c>
-      <c r="G556" t="inlineStr">
-        <is>
-          <t>e4ab8ac2-38c2-4dcc-83f1-654548629a50</t>
-        </is>
-      </c>
-    </row>
-    <row r="557">
-      <c r="A557" t="inlineStr">
-        <is>
-          <t>660edfc8ee2bf77136b3aef3</t>
-        </is>
-      </c>
-      <c r="B557" t="inlineStr">
-        <is>
-          <t>d429f630-d036-42d4-89d1-7c36465ac41d</t>
-        </is>
-      </c>
-      <c r="C557" t="inlineStr">
-        <is>
-          <t>word</t>
-        </is>
-      </c>
-      <c r="D557" t="inlineStr">
-        <is>
-          <t>ta</t>
-        </is>
-      </c>
-      <c r="E557" t="inlineStr">
-        <is>
-          <t>collectionId</t>
-        </is>
-      </c>
-      <c r="F557" t="inlineStr">
-        <is>
-          <t>61bc9579-0f9b-47ae-b446-7cdd525ce413</t>
-        </is>
-      </c>
-      <c r="G557" t="inlineStr">
-        <is>
-          <t>42259cda-9db5-4b0d-8589-880eb7c949b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="558">
-      <c r="A558" t="inlineStr">
-        <is>
-          <t>660edfc9ee2bf77136b3aefb</t>
-        </is>
-      </c>
-      <c r="B558" t="inlineStr">
-        <is>
-          <t>f20714c5-0a4a-46ca-a34d-6691964cb646</t>
-        </is>
-      </c>
-      <c r="C558" t="inlineStr">
-        <is>
-          <t>word</t>
-        </is>
-      </c>
-      <c r="D558" t="inlineStr">
-        <is>
-          <t>ta</t>
-        </is>
-      </c>
-      <c r="E558" t="inlineStr">
-        <is>
-          <t>collectionId</t>
-        </is>
-      </c>
-      <c r="F558" t="inlineStr">
-        <is>
-          <t>61bc9579-0f9b-47ae-b446-7cdd525ce413</t>
-        </is>
-      </c>
-      <c r="G558" t="inlineStr">
-        <is>
-          <t>42259cda-9db5-4b0d-8589-880eb7c949b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="559">
-      <c r="A559" t="inlineStr">
-        <is>
-          <t>660edfc9ee2bf77136b3aefd</t>
-        </is>
-      </c>
-      <c r="B559" t="inlineStr">
-        <is>
-          <t>99ad9963-e99c-4d4e-929a-6afeca3b1a9f</t>
-        </is>
-      </c>
-      <c r="C559" t="inlineStr">
-        <is>
-          <t>word</t>
-        </is>
-      </c>
-      <c r="D559" t="inlineStr">
-        <is>
-          <t>ta</t>
-        </is>
-      </c>
-      <c r="E559" t="inlineStr">
-        <is>
-          <t>collectionId</t>
-        </is>
-      </c>
-      <c r="F559" t="inlineStr">
-        <is>
-          <t>61bc9579-0f9b-47ae-b446-7cdd525ce413</t>
-        </is>
-      </c>
-      <c r="G559" t="inlineStr">
-        <is>
-          <t>42259cda-9db5-4b0d-8589-880eb7c949b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="560">
-      <c r="A560" t="inlineStr">
-        <is>
-          <t>660edfcdee2bf77136b3af01</t>
-        </is>
-      </c>
-      <c r="B560" t="inlineStr">
-        <is>
-          <t>bd357e23-20e6-480f-9bfd-3f147872f677</t>
-        </is>
-      </c>
-      <c r="C560" t="inlineStr">
-        <is>
-          <t>word</t>
-        </is>
-      </c>
-      <c r="D560" t="inlineStr">
-        <is>
-          <t>ta</t>
-        </is>
-      </c>
-      <c r="E560" t="inlineStr">
-        <is>
-          <t>collectionId</t>
-        </is>
-      </c>
-      <c r="F560" t="inlineStr">
-        <is>
-          <t>61bc9579-0f9b-47ae-b446-7cdd525ce413</t>
-        </is>
-      </c>
-      <c r="G560" t="inlineStr">
-        <is>
-          <t>42259cda-9db5-4b0d-8589-880eb7c949b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="561">
-      <c r="A561" t="inlineStr">
-        <is>
-          <t>660edfcdee2bf77136b3af05</t>
-        </is>
-      </c>
-      <c r="B561" t="inlineStr">
-        <is>
-          <t>05b4a940-10ad-4323-9f2c-21e2b9eee5b2</t>
-        </is>
-      </c>
-      <c r="C561" t="inlineStr">
-        <is>
-          <t>word</t>
-        </is>
-      </c>
-      <c r="D561" t="inlineStr">
-        <is>
-          <t>ta</t>
-        </is>
-      </c>
-      <c r="E561" t="inlineStr">
-        <is>
-          <t>collectionId</t>
-        </is>
-      </c>
-      <c r="F561" t="inlineStr">
-        <is>
-          <t>61bc9579-0f9b-47ae-b446-7cdd525ce413</t>
-        </is>
-      </c>
-      <c r="G561" t="inlineStr">
-        <is>
-          <t>42259cda-9db5-4b0d-8589-880eb7c949b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="562">
-      <c r="A562" t="inlineStr">
-        <is>
-          <t>660edfceee2bf77136b3af07</t>
-        </is>
-      </c>
-      <c r="B562" t="inlineStr">
-        <is>
-          <t>678b3712-58fd-489e-aace-d28827265a93</t>
-        </is>
-      </c>
-      <c r="C562" t="inlineStr">
-        <is>
-          <t>word</t>
-        </is>
-      </c>
-      <c r="D562" t="inlineStr">
-        <is>
-          <t>ta</t>
-        </is>
-      </c>
-      <c r="E562" t="inlineStr">
-        <is>
-          <t>collectionId</t>
-        </is>
-      </c>
-      <c r="F562" t="inlineStr">
-        <is>
-          <t>76ef507c-5d56-457c-aa3a-647cf5dba545</t>
-        </is>
-      </c>
-      <c r="G562" t="inlineStr">
-        <is>
-          <t>1efb5897-9eb3-4e71-8fd2-892a505d0dc9</t>
-        </is>
-      </c>
-    </row>
-    <row r="563">
-      <c r="A563" t="inlineStr">
-        <is>
-          <t>660edfceee2bf77136b3af09</t>
-        </is>
-      </c>
-      <c r="B563" t="inlineStr">
-        <is>
-          <t>b7b55c23-18fb-4e55-8838-ca285727f417</t>
-        </is>
-      </c>
-      <c r="C563" t="inlineStr">
-        <is>
-          <t>word</t>
-        </is>
-      </c>
-      <c r="D563" t="inlineStr">
-        <is>
-          <t>ta</t>
-        </is>
-      </c>
-      <c r="E563" t="inlineStr">
-        <is>
-          <t>collectionId</t>
-        </is>
-      </c>
-      <c r="F563" t="inlineStr">
-        <is>
-          <t>76ef507c-5d56-457c-aa3a-647cf5dba545</t>
-        </is>
-      </c>
-      <c r="G563" t="inlineStr">
-        <is>
-          <t>1efb5897-9eb3-4e71-8fd2-892a505d0dc9</t>
-        </is>
-      </c>
-    </row>
-    <row r="564">
-      <c r="A564" t="inlineStr">
-        <is>
-          <t>660edfceee2bf77136b3af0b</t>
-        </is>
-      </c>
-      <c r="B564" t="inlineStr">
-        <is>
-          <t>d2558e6e-234f-462d-956f-5c8d2ab83225</t>
-        </is>
-      </c>
-      <c r="C564" t="inlineStr">
-        <is>
-          <t>word</t>
-        </is>
-      </c>
-      <c r="D564" t="inlineStr">
-        <is>
-          <t>ta</t>
-        </is>
-      </c>
-      <c r="E564" t="inlineStr">
-        <is>
-          <t>collectionId</t>
-        </is>
-      </c>
-      <c r="F564" t="inlineStr">
-        <is>
-          <t>76ef507c-5d56-457c-aa3a-647cf5dba545</t>
-        </is>
-      </c>
-      <c r="G564" t="inlineStr">
-        <is>
-          <t>1efb5897-9eb3-4e71-8fd2-892a505d0dc9</t>
-        </is>
-      </c>
-    </row>
-    <row r="565">
-      <c r="A565" t="inlineStr">
-        <is>
-          <t>660edfcfee2bf77136b3af0f</t>
-        </is>
-      </c>
-      <c r="B565" t="inlineStr">
-        <is>
-          <t>f0f971a4-b0f8-4ffe-a2fb-03dc4dff9a58</t>
-        </is>
-      </c>
-      <c r="C565" t="inlineStr">
-        <is>
-          <t>word</t>
-        </is>
-      </c>
-      <c r="D565" t="inlineStr">
-        <is>
-          <t>ta</t>
-        </is>
-      </c>
-      <c r="E565" t="inlineStr">
-        <is>
-          <t>collectionId</t>
-        </is>
-      </c>
-      <c r="F565" t="inlineStr">
-        <is>
-          <t>76ef507c-5d56-457c-aa3a-647cf5dba545</t>
-        </is>
-      </c>
-      <c r="G565" t="inlineStr">
-        <is>
-          <t>1efb5897-9eb3-4e71-8fd2-892a505d0dc9</t>
-        </is>
-      </c>
-    </row>
-    <row r="566">
-      <c r="A566" t="inlineStr">
-        <is>
-          <t>660edfcfee2bf77136b3af13</t>
-        </is>
-      </c>
-      <c r="B566" t="inlineStr">
-        <is>
-          <t>31c40aa2-fef2-4137-9e3d-98e2679058d8</t>
-        </is>
-      </c>
-      <c r="C566" t="inlineStr">
-        <is>
-          <t>word</t>
-        </is>
-      </c>
-      <c r="D566" t="inlineStr">
-        <is>
-          <t>ta</t>
-        </is>
-      </c>
-      <c r="E566" t="inlineStr">
-        <is>
-          <t>collectionId</t>
-        </is>
-      </c>
-      <c r="F566" t="inlineStr">
-        <is>
-          <t>76ef507c-5d56-457c-aa3a-647cf5dba545</t>
-        </is>
-      </c>
-      <c r="G566" t="inlineStr">
-        <is>
-          <t>1efb5897-9eb3-4e71-8fd2-892a505d0dc9</t>
-        </is>
-      </c>
-    </row>
-    <row r="567">
-      <c r="A567" t="inlineStr">
-        <is>
-          <t>660edfd0ee2bf77136b3af1d</t>
-        </is>
-      </c>
-      <c r="B567" t="inlineStr">
-        <is>
-          <t>f0880412-5a96-4a31-b54e-1c3bfd7d3cdf</t>
-        </is>
-      </c>
-      <c r="C567" t="inlineStr">
-        <is>
-          <t>word</t>
-        </is>
-      </c>
-      <c r="D567" t="inlineStr">
-        <is>
-          <t>ta</t>
-        </is>
-      </c>
-      <c r="E567" t="inlineStr">
-        <is>
-          <t>collectionId</t>
-        </is>
-      </c>
-      <c r="F567" t="inlineStr">
-        <is>
-          <t>55767bfa-0e12-4d8f-999b-e84daf6c7587</t>
-        </is>
-      </c>
-      <c r="G567" t="inlineStr">
-        <is>
-          <t>aca41722-3f1e-45eb-a563-4d79c27aa50e</t>
-        </is>
-      </c>
-    </row>
-    <row r="568">
-      <c r="A568" t="inlineStr">
-        <is>
-          <t>660edfd0ee2bf77136b3af1f</t>
-        </is>
-      </c>
-      <c r="B568" t="inlineStr">
-        <is>
-          <t>b116168e-020c-4512-ac2c-7c5b4ab8025f</t>
-        </is>
-      </c>
-      <c r="C568" t="inlineStr">
-        <is>
-          <t>word</t>
-        </is>
-      </c>
-      <c r="D568" t="inlineStr">
-        <is>
-          <t>ta</t>
-        </is>
-      </c>
-      <c r="E568" t="inlineStr">
-        <is>
-          <t>collectionId</t>
-        </is>
-      </c>
-      <c r="F568" t="inlineStr">
-        <is>
-          <t>55767bfa-0e12-4d8f-999b-e84daf6c7587</t>
-        </is>
-      </c>
-      <c r="G568" t="inlineStr">
-        <is>
-          <t>aca41722-3f1e-45eb-a563-4d79c27aa50e</t>
-        </is>
-      </c>
-    </row>
-    <row r="569">
-      <c r="A569" t="inlineStr">
-        <is>
-          <t>660edfd1ee2bf77136b3af23</t>
-        </is>
-      </c>
-      <c r="B569" t="inlineStr">
-        <is>
-          <t>b88fc6d4-42c8-490c-a6eb-eaf378bf482b</t>
-        </is>
-      </c>
-      <c r="C569" t="inlineStr">
-        <is>
-          <t>word</t>
-        </is>
-      </c>
-      <c r="D569" t="inlineStr">
-        <is>
-          <t>ta</t>
-        </is>
-      </c>
-      <c r="E569" t="inlineStr">
-        <is>
-          <t>collectionId</t>
-        </is>
-      </c>
-      <c r="F569" t="inlineStr">
-        <is>
-          <t>55767bfa-0e12-4d8f-999b-e84daf6c7587</t>
-        </is>
-      </c>
-      <c r="G569" t="inlineStr">
-        <is>
-          <t>aca41722-3f1e-45eb-a563-4d79c27aa50e</t>
-        </is>
-      </c>
-    </row>
-    <row r="570">
-      <c r="A570" t="inlineStr">
-        <is>
-          <t>660edfd2ee2bf77136b3af29</t>
-        </is>
-      </c>
-      <c r="B570" t="inlineStr">
-        <is>
-          <t>a4590294-4bba-4a73-95ec-44b5f2d2a37a</t>
-        </is>
-      </c>
-      <c r="C570" t="inlineStr">
-        <is>
-          <t>word</t>
-        </is>
-      </c>
-      <c r="D570" t="inlineStr">
-        <is>
-          <t>ta</t>
-        </is>
-      </c>
-      <c r="E570" t="inlineStr">
-        <is>
-          <t>collectionId</t>
-        </is>
-      </c>
-      <c r="F570" t="inlineStr">
-        <is>
-          <t>55767bfa-0e12-4d8f-999b-e84daf6c7587</t>
-        </is>
-      </c>
-      <c r="G570" t="inlineStr">
-        <is>
-          <t>aca41722-3f1e-45eb-a563-4d79c27aa50e</t>
-        </is>
-      </c>
-    </row>
-    <row r="571">
-      <c r="A571" t="inlineStr">
-        <is>
-          <t>660edfd2ee2bf77136b3af2b</t>
-        </is>
-      </c>
-      <c r="B571" t="inlineStr">
-        <is>
-          <t>9c592467-7d46-4dc0-afe1-abe6141b788e</t>
-        </is>
-      </c>
-      <c r="C571" t="inlineStr">
-        <is>
-          <t>word</t>
-        </is>
-      </c>
-      <c r="D571" t="inlineStr">
-        <is>
-          <t>ta</t>
-        </is>
-      </c>
-      <c r="E571" t="inlineStr">
-        <is>
-          <t>collectionId</t>
-        </is>
-      </c>
-      <c r="F571" t="inlineStr">
-        <is>
-          <t>55767bfa-0e12-4d8f-999b-e84daf6c7587</t>
-        </is>
-      </c>
-      <c r="G571" t="inlineStr">
-        <is>
-          <t>aca41722-3f1e-45eb-a563-4d79c27aa50e</t>
-        </is>
-      </c>
-    </row>
-    <row r="572">
-      <c r="A572" t="inlineStr">
-        <is>
-          <t>6647557a2740a348c116e889</t>
-        </is>
-      </c>
-      <c r="B572" t="inlineStr">
-        <is>
-          <t>e6e3fa31-2c92-45a4-bc73-e148f9a71946</t>
-        </is>
-      </c>
-      <c r="C572" t="inlineStr">
-        <is>
-          <t>sentence</t>
-        </is>
-      </c>
-      <c r="D572" t="inlineStr">
-        <is>
-          <t>ta</t>
-        </is>
-      </c>
-      <c r="E572" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F572" t="inlineStr">
-        <is>
-          <t xml:space="preserve">அவர்களுடன்‌ கபடி, கண்ணாமூச்சி, கயிறு தாண்டுதல்‌, விளையாடியதை எண்ணி ஏங்கினான்‌. </t>
-        </is>
-      </c>
-      <c r="G572" t="inlineStr"/>
-    </row>
-    <row r="573">
-      <c r="A573" t="inlineStr">
-        <is>
-          <t>664755862740a348c116e8a3</t>
-        </is>
-      </c>
-      <c r="B573" t="inlineStr">
-        <is>
-          <t>4b9a8d81-0818-442e-877f-c00387564c09</t>
-        </is>
-      </c>
-      <c r="C573" t="inlineStr">
-        <is>
-          <t>sentence</t>
-        </is>
-      </c>
-      <c r="D573" t="inlineStr">
-        <is>
-          <t>ta</t>
-        </is>
-      </c>
-      <c r="E573" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F573" t="inlineStr">
-        <is>
           <t xml:space="preserve">அவளை ஆசிரியர்கள்‌ அனைவரும்‌ மிகவும் பாராட்டினர்‌. </t>
         </is>
       </c>
-      <c r="G573" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>
